--- a/src/attributions/attributions_saliency_traj_444.xlsx
+++ b/src/attributions/attributions_saliency_traj_444.xlsx
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.002599120372906327</v>
+        <v>7.547067137902985e-11</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01609206385910511</v>
+        <v>3.818514116016303e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0012603176292032</v>
+        <v>2.376350227706325e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004631020594388247</v>
+        <v>6.787637674143809e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00521476287394762</v>
+        <v>8.687022767794872e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008975524455308914</v>
+        <v>1.030679763758258e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0009215386817231774</v>
+        <v>1.036766505979614e-11</v>
       </c>
       <c r="H2" t="n">
-        <v>0.009912168607115746</v>
+        <v>7.4386566351059e-11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02048457227647305</v>
+        <v>6.472564151316362e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004406089894473553</v>
+        <v>1.942199734372707e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01250215247273445</v>
+        <v>9.805785072813933e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002390267327427864</v>
+        <v>1.222475870532591e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01054298505187035</v>
+        <v>8.801188666751614e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0003593885339796543</v>
+        <v>1.232246749083288e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>0.008589151315391064</v>
+        <v>1.214284894857087e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002112683607265353</v>
+        <v>5.991619422829331e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.006170693784952164</v>
+        <v>2.847440616626784e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01722599938511848</v>
+        <v>5.492521992778165e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00115384953096509</v>
+        <v>2.791348263642135e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>0.000333341071382165</v>
+        <v>1.608746746928347e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0006649932474829257</v>
+        <v>2.652849814821501e-11</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001044812495820224</v>
+        <v>3.83237219736543e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0003954970161430538</v>
+        <v>2.837692580914819e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00529852882027626</v>
+        <v>3.359212907838582e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.985466173617169e-05</v>
+        <v>3.099403234063658e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001011194195598364</v>
+        <v>1.368831992198949e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001200702507048845</v>
+        <v>7.042699756709681e-11</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003122310154139996</v>
+        <v>1.82547726934601e-10</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0009371086489409208</v>
+        <v>1.115605871571113e-10</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.006151573732495308</v>
+        <v>4.885957749500847e-10</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.001752619631588459</v>
+        <v>7.792496647951452e-10</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.001569732907228172</v>
+        <v>5.461041063803407e-10</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.002420732052996755</v>
+        <v>5.495593563553669e-11</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.002858974970877171</v>
+        <v>4.136728459780414e-11</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.003361525014042854</v>
+        <v>7.70429331442557e-10</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.0007508508861064911</v>
+        <v>5.352180365569836e-10</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.002070586662739515</v>
+        <v>2.808134558218711e-10</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.001962702721357346</v>
+        <v>6.94173815651844e-11</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.001967809163033962</v>
+        <v>1.614837707997197e-10</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.0006330799078568816</v>
+        <v>1.809091765281323e-11</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.002716755727306008</v>
+        <v>3.804404569152098e-10</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.0001896416069939733</v>
+        <v>5.277305675788213e-11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.002010888652876019</v>
+        <v>4.65856853093527e-10</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.003169203409925103</v>
+        <v>8.879740692746552e-11</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.002508729230612516</v>
+        <v>8.825244701693435e-11</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.002498976420611143</v>
+        <v>1.259894827354557e-10</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.01644771359860897</v>
+        <v>1.678872374455409e-09</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.001306418562307954</v>
+        <v>4.948624496292631e-11</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.0008289782563224435</v>
+        <v>3.140839255344474e-10</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.01308901887387037</v>
+        <v>3.317455754547893e-10</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.001085194759070873</v>
+        <v>1.039999683594139e-10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.004983411636203527</v>
+        <v>1.024904744406641e-10</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.490161806344986e-07</v>
+        <v>3.657084635122487e-10</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.00444947462528944</v>
+        <v>2.487176853360751e-10</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.001066455733962357</v>
+        <v>9.085728697177942e-11</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.002096116077154875</v>
+        <v>4.80215089915248e-10</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.0005662792827934027</v>
+        <v>7.157971437798949e-11</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.0002756011381279677</v>
+        <v>6.268913166351808e-10</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.002283708192408085</v>
+        <v>6.066880331445645e-10</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.008568987250328064</v>
+        <v>5.367234989783753e-10</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.001391954370774329</v>
+        <v>1.22320958917399e-10</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.003100564237684011</v>
+        <v>2.998943038345914e-10</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.01441813632845879</v>
+        <v>7.903755427918213e-11</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.001354834530502558</v>
+        <v>3.443210716547185e-10</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.001012637279927731</v>
+        <v>5.740439790180574e-10</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.001616248511709273</v>
+        <v>8.081219027289421e-11</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.0006262115202844143</v>
+        <v>1.999016924214558e-10</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.01306765247136354</v>
+        <v>4.911778761496066e-10</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.001577193499542773</v>
+        <v>4.112082618856761e-10</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.004680970218032598</v>
+        <v>7.111610189625139e-10</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.0006572737474925816</v>
+        <v>1.458850401592215e-10</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.005301559343934059</v>
+        <v>3.528400349672722e-10</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.0008789283456280828</v>
+        <v>9.987375509945551e-12</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.008966622874140739</v>
+        <v>5.492881705038144e-10</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.003562293946743011</v>
+        <v>2.364894946538243e-10</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.001447304617613554</v>
+        <v>1.24515869837083e-10</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.002009303076192737</v>
+        <v>4.696887878630207e-10</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.0001214928925037384</v>
+        <v>4.10110667647956e-10</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.0007589847664348781</v>
+        <v>1.999741344738126e-10</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.001020070980302989</v>
+        <v>2.52715764981204e-10</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.001393619691953063</v>
+        <v>1.571974217462468e-10</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0004609489697031677</v>
+        <v>1.56711074672522e-10</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.002498300513252616</v>
+        <v>1.584695985545892e-10</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.001515249954536557</v>
+        <v>2.669535426047531e-11</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.000534356280695647</v>
+        <v>3.979886142868594e-10</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.0009200162021443248</v>
+        <v>2.330114157178542e-10</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.0005672386614605784</v>
+        <v>2.625927808530548e-10</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.001260992255993187</v>
+        <v>1.851037795264077e-10</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.001834739930927753</v>
+        <v>4.938069484566876e-12</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.004849852062761784</v>
+        <v>1.853570352761125e-10</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.006604696623980999</v>
+        <v>3.577761975570581e-10</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.002249553333967924</v>
+        <v>9.395769717812641e-10</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.0004855940933339298</v>
+        <v>1.139727756616082e-10</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.006134207360446453</v>
+        <v>3.423815952974252e-10</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.004950510337948799</v>
+        <v>4.539311149187597e-10</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.002717267023399472</v>
+        <v>4.663229247192646e-10</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.002049675676971674</v>
+        <v>8.393397088468646e-11</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.006320544518530369</v>
+        <v>5.204503494837809e-12</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.001992864534258842</v>
+        <v>6.753107795187674e-11</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.0003872924426104873</v>
+        <v>2.43793374377077e-10</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.002942485269159079</v>
+        <v>1.744497324374095e-10</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.001131512108258903</v>
+        <v>4.528952907145722e-11</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.0001734709949232638</v>
+        <v>3.339705179072894e-10</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.0005927192978560925</v>
+        <v>1.248621483984635e-10</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.360394526273012e-05</v>
+        <v>2.928579045935464e-10</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.001276399823836982</v>
+        <v>9.01650004658805e-11</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.001622605137526989</v>
+        <v>8.909691734393377e-11</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.003786505432799459</v>
+        <v>1.953785466746183e-10</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.001327963313087821</v>
+        <v>2.431246870493453e-10</v>
       </c>
       <c r="DF2" t="n">
-        <v>5.96360769122839e-05</v>
+        <v>5.024821531085522e-11</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.004209212493151426</v>
+        <v>1.914333830344006e-10</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.001652825274504721</v>
+        <v>5.335651365179217e-11</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.0007756390841677785</v>
+        <v>1.753927281189505e-10</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.0007681823917664587</v>
+        <v>3.943836923703259e-11</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.00308147631585598</v>
+        <v>3.62807756060235e-10</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.00882299430668354</v>
+        <v>3.33276600761323e-10</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.0014925078721717</v>
+        <v>1.473019622943994e-11</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.0008959921542555094</v>
+        <v>1.205177069252272e-10</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.0007678805268369615</v>
+        <v>8.997075306993452e-11</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.002330253832042217</v>
+        <v>1.528380200177537e-10</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.001081337919458747</v>
+        <v>7.086484177243335e-10</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.0003062081523239613</v>
+        <v>4.245336582275883e-10</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.0007489104173146188</v>
+        <v>4.262525887810398e-10</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.003268005792051554</v>
+        <v>1.523076664788903e-10</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.0006251807790249586</v>
+        <v>3.385775548814252e-10</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.003276385832577944</v>
+        <v>1.039408836778222e-10</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.0003336823137942702</v>
+        <v>2.443386604156217e-10</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.005583182908594608</v>
+        <v>2.229677692477949e-10</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.0008420111844316125</v>
+        <v>1.987656012003569e-10</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.002528143581002951</v>
+        <v>1.957638495753145e-10</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.0005038821836933494</v>
+        <v>1.264620907992509e-10</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.002193921245634556</v>
+        <v>2.931090925528679e-10</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.002054056851193309</v>
+        <v>4.92685892083955e-11</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.004381606355309486</v>
+        <v>4.373003625879335e-10</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.001051481813192368</v>
+        <v>2.080494387879384e-10</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.001227070693857968</v>
+        <v>3.085836586258495e-10</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.002749964594841003</v>
+        <v>5.897538707388961e-11</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.002321261679753661</v>
+        <v>5.337392680604403e-11</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.001046667573973536</v>
+        <v>3.62077923199422e-10</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.0005836933851242065</v>
+        <v>1.486139405981746e-10</v>
       </c>
       <c r="EK2" t="n">
-        <v>2.801614755298942e-05</v>
+        <v>1.30266700204551e-10</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.003058141097426414</v>
+        <v>7.692303738426887e-11</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.0005427438882179558</v>
+        <v>7.399306167776842e-11</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.004869779106229544</v>
+        <v>1.473213495639669e-10</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.001119884545914829</v>
+        <v>8.188044686718854e-11</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.002458132337778807</v>
+        <v>1.393778703562276e-10</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.001337280380539596</v>
+        <v>1.696216778146464e-10</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.0004368243389762938</v>
+        <v>9.774973885878779e-11</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.003626642283052206</v>
+        <v>2.003133214856234e-10</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.003126605181023479</v>
+        <v>3.211001742275954e-10</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.002832961268723011</v>
+        <v>2.047156749673817e-10</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.003603304736316204</v>
+        <v>2.431369550137674e-10</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.003897603834047914</v>
+        <v>1.345730332724671e-10</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.0002665995270945132</v>
+        <v>2.382454789007227e-10</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.003453490789979696</v>
+        <v>2.415337652106331e-10</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.001015160931274295</v>
+        <v>4.169964373801349e-11</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.001114983228035271</v>
+        <v>3.717001983982726e-10</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.0002146267361240461</v>
+        <v>2.013991889926459e-10</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.001097046886570752</v>
+        <v>2.024938827727141e-10</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.001399491913616657</v>
+        <v>1.36017391794141e-10</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.001026872312650084</v>
+        <v>3.962667347034987e-11</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.00391002930700779</v>
+        <v>1.449410869103218e-10</v>
       </c>
       <c r="FG2" t="n">
-        <v>1.457198231946677e-05</v>
+        <v>3.532684977880507e-10</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.001082260627299547</v>
+        <v>2.24592205944063e-10</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.00139045063406229</v>
+        <v>5.923701112964253e-11</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.002423689467832446</v>
+        <v>9.11581019003016e-11</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.005656545050442219</v>
+        <v>1.604173044400525e-10</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.0005797549383714795</v>
+        <v>2.899278317425313e-10</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.0009179430198855698</v>
+        <v>1.477403616112483e-10</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.001555354334414005</v>
+        <v>2.096440243626319e-10</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.0004512912128120661</v>
+        <v>2.401473742086324e-10</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.001033767824992537</v>
+        <v>5.144903392206857e-10</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.002119699958711863</v>
+        <v>6.955256370844154e-10</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.001001637428998947</v>
+        <v>3.147055671615107e-10</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.0009376385132782161</v>
+        <v>1.693204187969144e-10</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.00387727003544569</v>
+        <v>1.296894813762606e-10</v>
       </c>
       <c r="FU2" t="n">
-        <v>8.450579480268061e-05</v>
+        <v>1.196460569508062e-10</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.006723211146891117</v>
+        <v>1.972568081098913e-10</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.0006700553931295872</v>
+        <v>1.794748932804069e-10</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.0004415071452967823</v>
+        <v>6.556751669384298e-11</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.002901530591771007</v>
+        <v>2.715506985939697e-10</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.001217569690197706</v>
+        <v>9.842653081459929e-11</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.001031131716445088</v>
+        <v>9.471334827537703e-11</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.003619985189288855</v>
+        <v>1.980919039912266e-10</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.001564617967233062</v>
+        <v>1.70452124637066e-10</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.0043830256909132</v>
+        <v>3.833398876107452e-10</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.002817362081259489</v>
+        <v>4.44194611648463e-11</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.0009326980798505247</v>
+        <v>1.488100892510502e-10</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.0007584390114061534</v>
+        <v>8.577309001944755e-11</v>
       </c>
     </row>
     <row r="3">
@@ -2706,571 +2706,571 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.001826437306590378</v>
+        <v>2.927897854720918e-11</v>
       </c>
       <c r="B5" t="n">
-        <v>0.03024758584797382</v>
+        <v>4.775094208930852e-11</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003799000987783074</v>
+        <v>1.619124972984665e-11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008706137537956238</v>
+        <v>4.957690508122781e-11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002584209432825446</v>
+        <v>1.710889242778624e-11</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001737460726872087</v>
+        <v>5.443042284253297e-12</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007181717548519373</v>
+        <v>4.492904659425534e-11</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004537832923233509</v>
+        <v>6.526034573850481e-11</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003134252037853003</v>
+        <v>1.748337238871578e-11</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00600776681676507</v>
+        <v>1.833502620562921e-11</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02421927638351917</v>
+        <v>4.70443579925206e-11</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004565797746181488</v>
+        <v>1.225301023838332e-11</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01309492159634829</v>
+        <v>1.024987907050079e-11</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00546382088214159</v>
+        <v>2.017617843630415e-11</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006927585229277611</v>
+        <v>2.03953260530243e-12</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006485254503786564</v>
+        <v>5.692324042683161e-11</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.688141290098429e-05</v>
+        <v>4.77773584584007e-11</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002411410678178072</v>
+        <v>2.978033791789514e-11</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003521543461829424</v>
+        <v>3.233701154070623e-11</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004729864653199911</v>
+        <v>2.615369899816589e-11</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002297791186720133</v>
+        <v>2.642662998153522e-11</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003025323385372758</v>
+        <v>4.012111129436668e-11</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004525301977992058</v>
+        <v>6.447165284279022e-12</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004895764868706465</v>
+        <v>5.560485231981271e-12</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001069940772140399</v>
+        <v>4.632757719114089e-12</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002825890900567174</v>
+        <v>1.794525465725894e-12</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00165717292111367</v>
+        <v>2.754879310784553e-11</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003214523894712329</v>
+        <v>6.230693738729087e-11</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.006482399068772793</v>
+        <v>2.555430346495857e-11</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.003886079881340265</v>
+        <v>3.020336411529989e-11</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.001851965440437198</v>
+        <v>2.531084369872261e-11</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0009761007386259735</v>
+        <v>2.330199228017804e-11</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.001140790758654475</v>
+        <v>8.564455568349505e-12</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0001369877136312425</v>
+        <v>7.571498115976905e-12</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.006057932041585445</v>
+        <v>1.998744746101178e-11</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0001041601717588492</v>
+        <v>5.615136827730183e-12</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.002803369192406535</v>
+        <v>1.476958312596199e-11</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.003503491869196296</v>
+        <v>2.695369968885863e-13</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0006218196358531713</v>
+        <v>4.94991244173737e-12</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.002815695013850927</v>
+        <v>3.584138541512516e-11</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.001322350464761257</v>
+        <v>4.18098507204423e-11</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.001133944955654442</v>
+        <v>2.713890050187739e-11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0007687300676479936</v>
+        <v>2.202135696016683e-11</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0009618987096473575</v>
+        <v>2.022372200261024e-11</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.001996946521103382</v>
+        <v>1.762715667874559e-11</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.002661773236468434</v>
+        <v>2.807051683109685e-12</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.01984619535505772</v>
+        <v>3.568246739749092e-11</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.003081000875681639</v>
+        <v>1.500200137727337e-11</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.004953842144459486</v>
+        <v>1.85763036897324e-11</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.00367784989066422</v>
+        <v>4.996034141946382e-11</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0002092598006129265</v>
+        <v>2.618125855002873e-11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.008261994458734989</v>
+        <v>2.215209439493382e-11</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0008727512322366238</v>
+        <v>1.853540931850972e-11</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.0006874117534607649</v>
+        <v>1.78199434375248e-11</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0002690692199394107</v>
+        <v>6.019729853479205e-12</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.008221559226512909</v>
+        <v>6.450858510559376e-12</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.007280182559043169</v>
+        <v>3.336544929233298e-11</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.003237232100218534</v>
+        <v>4.03936606385713e-11</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.005738941021263599</v>
+        <v>4.877321810314861e-11</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.00164468795992434</v>
+        <v>2.414780181370091e-11</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.001796250930055976</v>
+        <v>2.937543958081434e-11</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.001775237731635571</v>
+        <v>1.43300163402138e-11</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.002081130165606737</v>
+        <v>6.402653407455716e-11</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.001566313672810793</v>
+        <v>6.321221324157023e-12</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.001253301743417978</v>
+        <v>3.67986752181082e-11</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.001920696580782533</v>
+        <v>1.388560447179721e-11</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0018117087893188</v>
+        <v>8.491657897680138e-12</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.005890168715268373</v>
+        <v>3.363457429239602e-11</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.002889168448746204</v>
+        <v>5.648802606228465e-12</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.003356824163347483</v>
+        <v>4.08358485914917e-11</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.007952075451612473</v>
+        <v>5.049552356112263e-13</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.000328941154293716</v>
+        <v>6.810468421852844e-12</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0003994885191787034</v>
+        <v>1.525509579769491e-11</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.00913886446505785</v>
+        <v>1.876828553681875e-12</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.004308202303946018</v>
+        <v>1.816970532364515e-11</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.002279953099787235</v>
+        <v>2.794854625509657e-11</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.001909691607579589</v>
+        <v>2.931566794872609e-11</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0003761895932257175</v>
+        <v>1.038711000891923e-12</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.00325833959504962</v>
+        <v>6.327630086566671e-11</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.003429859410971403</v>
+        <v>7.735622906124284e-12</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0005426693824119866</v>
+        <v>4.854498964271259e-13</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.0001846840896178037</v>
+        <v>3.417490899645936e-12</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.005330335348844528</v>
+        <v>1.690821961608524e-12</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.00197182921692729</v>
+        <v>2.05348724136023e-11</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0005861129029653966</v>
+        <v>3.300095223132682e-12</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.0004955742042511702</v>
+        <v>3.174968100927433e-12</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0003574063302949071</v>
+        <v>2.598231959444197e-13</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.002086637541651726</v>
+        <v>7.973795235205472e-12</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0006897527491673827</v>
+        <v>1.009288139175446e-11</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.001030670013278723</v>
+        <v>6.518309329794914e-12</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.005537683144211769</v>
+        <v>3.458091799024565e-11</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.00421430915594101</v>
+        <v>4.744173803805651e-11</v>
       </c>
       <c r="CO5" t="n">
-        <v>7.037515752017498e-05</v>
+        <v>1.365539972764118e-11</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.008078422397375107</v>
+        <v>2.390184924982997e-11</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.006158165633678436</v>
+        <v>4.738570300033551e-11</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.000598643091507256</v>
+        <v>9.466717340589348e-12</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.001979437889531255</v>
+        <v>2.450381217378172e-11</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0004428183019626886</v>
+        <v>2.598822199106898e-11</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0004315710975788534</v>
+        <v>3.360654809991814e-11</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0005565036553889513</v>
+        <v>4.233137278208954e-12</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.004996536299586296</v>
+        <v>1.192785367004623e-11</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.002190787810832262</v>
+        <v>2.045580545229075e-11</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.002594375051558018</v>
+        <v>3.071930730624839e-13</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.001675865729339421</v>
+        <v>5.841614518498073e-12</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0002371507143834606</v>
+        <v>4.000651806362887e-14</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.00243843742646277</v>
+        <v>7.505825388304244e-13</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0004818909510504454</v>
+        <v>8.364948490824364e-12</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.001300791976973414</v>
+        <v>3.783972267468183e-12</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.003886770457029343</v>
+        <v>1.216456969876933e-11</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0006905010668560863</v>
+        <v>6.52660260905269e-12</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.001466666348278522</v>
+        <v>6.739386826382088e-11</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.001445933361537755</v>
+        <v>6.468407059978531e-11</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.001709290663711727</v>
+        <v>4.291858535232507e-11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.0009321810211986303</v>
+        <v>3.641921833552608e-14</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.002623571781441569</v>
+        <v>5.726833243735463e-11</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.004225106909871101</v>
+        <v>1.882534753083753e-11</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.003110970836132765</v>
+        <v>4.689346133623928e-12</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.004167319741100073</v>
+        <v>2.560678752372425e-11</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0005601111333817244</v>
+        <v>1.105217826979921e-11</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.003528842469677329</v>
+        <v>1.079193678865664e-11</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.00142837013117969</v>
+        <v>2.166642559808807e-11</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.002347118221223354</v>
+        <v>3.953327248895633e-11</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.00122810760512948</v>
+        <v>2.289163997248878e-11</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.001361087546683848</v>
+        <v>9.632522210423211e-12</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0002212547697126865</v>
+        <v>1.702810982495695e-11</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.001670109573751688</v>
+        <v>2.012160056630297e-11</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0005109201883897185</v>
+        <v>1.632190736733374e-11</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.00667637912556529</v>
+        <v>6.038797240037752e-11</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0004030580457765609</v>
+        <v>4.333082156970924e-11</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.002635735552757978</v>
+        <v>5.303159300584781e-11</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.002673079026862979</v>
+        <v>2.038159571671194e-12</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.001012965571135283</v>
+        <v>3.483213717458966e-11</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.000296586484182626</v>
+        <v>2.281693063654888e-11</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.002685835584998131</v>
+        <v>1.645339246791888e-11</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.001060701906681061</v>
+        <v>6.923860790264413e-12</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0001938121858984232</v>
+        <v>7.665301726689222e-11</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.004245321732014418</v>
+        <v>3.799932243864212e-11</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.001650518155656755</v>
+        <v>2.610394712887487e-11</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.001499074744060636</v>
+        <v>6.243218182017118e-12</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.00019830372184515</v>
+        <v>7.01372467049044e-12</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0004009453114122152</v>
+        <v>4.555379077425536e-12</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.004295014776289463</v>
+        <v>1.692309833933869e-11</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.0004105728003196418</v>
+        <v>1.227091692146409e-11</v>
       </c>
       <c r="EN5" t="n">
-        <v>3.244564868509769e-05</v>
+        <v>3.74518471790708e-12</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.002897517522796988</v>
+        <v>1.677602154415148e-11</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.002514493884518743</v>
+        <v>2.355078285165568e-11</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.003469395916908979</v>
+        <v>1.298980714659059e-11</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.002529290737584233</v>
+        <v>6.029210984637157e-12</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.003927554003894329</v>
+        <v>1.672068906943824e-11</v>
       </c>
       <c r="ET5" t="n">
-        <v>4.031031858175993e-05</v>
+        <v>2.453775377331269e-11</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.002405981998890638</v>
+        <v>4.057004732160863e-12</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.003372378181666136</v>
+        <v>1.540115777964868e-11</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.0003610366838984191</v>
+        <v>4.840526417193569e-12</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.001483325846493244</v>
+        <v>1.626474562671509e-12</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.005361238960176706</v>
+        <v>2.678064367489519e-12</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.001364431576803327</v>
+        <v>2.347894274834506e-11</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.001213089330121875</v>
+        <v>6.802391115667827e-12</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.002107033738866448</v>
+        <v>9.251929951326066e-12</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0009493264369666576</v>
+        <v>3.884212829846634e-12</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.002837501000612974</v>
+        <v>4.754239103094138e-12</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.001258496544323862</v>
+        <v>8.949417595882636e-12</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.001812247559428215</v>
+        <v>2.026660740270247e-12</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.001728770439513028</v>
+        <v>1.052776789356447e-11</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0005920404801145196</v>
+        <v>3.463583933549508e-11</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.003186834743246436</v>
+        <v>9.273574963497566e-12</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.001968624070286751</v>
+        <v>3.616432457317909e-12</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.004251133650541306</v>
+        <v>1.875893711200671e-11</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.003131769131869078</v>
+        <v>3.992922659179499e-11</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0003885240294039249</v>
+        <v>9.209370245566451e-12</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.003194438759237528</v>
+        <v>6.356577070265601e-11</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.00379328872077167</v>
+        <v>4.403833894772724e-11</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.004120262339711189</v>
+        <v>2.485069441893195e-11</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.005455686245113611</v>
+        <v>7.048645694895939e-11</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.001374259009025991</v>
+        <v>3.572998147349793e-11</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.002230421639978886</v>
+        <v>1.444211070178447e-11</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.005986940115690231</v>
+        <v>3.589691391359118e-11</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.003066572826355696</v>
+        <v>5.017570386955938e-11</v>
       </c>
       <c r="FV5" t="n">
-        <v>4.979330697096884e-05</v>
+        <v>4.164447259258353e-11</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.006440386176109314</v>
+        <v>1.01794156437407e-10</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.001505691441707313</v>
+        <v>1.560258519606172e-11</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.006108001805841923</v>
+        <v>1.229420992093777e-11</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.00100701255723834</v>
+        <v>1.183709120305965e-11</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.001395421917550266</v>
+        <v>3.633910186651157e-11</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.000920414284337312</v>
+        <v>3.225452196997658e-11</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.001269027823582292</v>
+        <v>3.614378588090439e-11</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.004690374247729778</v>
+        <v>1.385391714542328e-11</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.006570311263203621</v>
+        <v>3.66456257699932e-12</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.003767029847949743</v>
+        <v>3.851135989968446e-13</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.001908453297801316</v>
+        <v>1.776509495066136e-11</v>
       </c>
     </row>
     <row r="6">
@@ -3844,1140 +3844,1140 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.02818325161933899</v>
+        <v>0.07756278663873672</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2596421241760254</v>
+        <v>0.309671014547348</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005296446848660707</v>
+        <v>0.1392316520214081</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1868983805179596</v>
+        <v>0.2159270346164703</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02852121740579605</v>
+        <v>0.1407337933778763</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001040209084749222</v>
+        <v>0.03029424324631691</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03269913792610168</v>
+        <v>0.1401319205760956</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02363956719636917</v>
+        <v>0.0578286200761795</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04864060506224632</v>
+        <v>0.07292941957712173</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06052296608686447</v>
+        <v>0.07456408441066742</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2191426903009415</v>
+        <v>0.3819738626480103</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01589564979076385</v>
+        <v>0.1495981365442276</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1774753481149673</v>
+        <v>0.2932141721248627</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06792730093002319</v>
+        <v>0.1950359791517258</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03992633521556854</v>
+        <v>0.003313349559903145</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02048132941126823</v>
+        <v>0.06367272883653641</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.032915860414505</v>
+        <v>0.1920337080955505</v>
       </c>
       <c r="R7" t="n">
-        <v>0.04595163464546204</v>
+        <v>0.05296493694186211</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01333107613027096</v>
+        <v>0.02161330170929432</v>
       </c>
       <c r="T7" t="n">
-        <v>0.02671300806105137</v>
+        <v>0.08735963702201843</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02647821418941021</v>
+        <v>0.1135141476988792</v>
       </c>
       <c r="V7" t="n">
-        <v>0.007185827475041151</v>
+        <v>0.01005209796130657</v>
       </c>
       <c r="W7" t="n">
-        <v>0.04088367521762848</v>
+        <v>0.002755774185061455</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01236523501574993</v>
+        <v>0.06374197453260422</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.04263376444578171</v>
+        <v>0.007508030161261559</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0296536348760128</v>
+        <v>0.001803749240934849</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02681439369916916</v>
+        <v>0.08582775294780731</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.05257273837924004</v>
+        <v>0.06220944225788116</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.03666165098547935</v>
+        <v>0.0445585623383522</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.005144194699823856</v>
+        <v>0.03467318788170815</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.02577085420489311</v>
+        <v>0.1972135603427887</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.04635240137577057</v>
+        <v>0.002622688189148903</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.04660842195153236</v>
+        <v>0.2068794369697571</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.01994650438427925</v>
+        <v>0.04641302675008774</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0323302336037159</v>
+        <v>0.06799576431512833</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.007281056605279446</v>
+        <v>0.004371056333184242</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.01274089422076941</v>
+        <v>0.006799258291721344</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01300918497145176</v>
+        <v>0.1941728293895721</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.01054388284683228</v>
+        <v>0.1200530156493187</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.008425729349255562</v>
+        <v>0.03594082221388817</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.01094702538102865</v>
+        <v>0.1337009519338608</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.008640872314572334</v>
+        <v>0.03732635825872421</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.01633714884519577</v>
+        <v>0.01335055753588676</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0008805142715573311</v>
+        <v>0.01699207723140717</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.009574113413691521</v>
+        <v>0.007205728441476822</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.03892796486616135</v>
+        <v>0.004555613733828068</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1604516208171844</v>
+        <v>0.2776342630386353</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.04131552204489708</v>
+        <v>0.07098252326250076</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.04727865383028984</v>
+        <v>0.1157882139086723</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.007848723791539669</v>
+        <v>0.06544311344623566</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.01030170544981956</v>
+        <v>0.05522561818361282</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.003132431767880917</v>
+        <v>0.005822530016303062</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.02447286993265152</v>
+        <v>0.04264068603515625</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.01113622263073921</v>
+        <v>0.01038775220513344</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0151298176497221</v>
+        <v>0.06582128256559372</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.05511857196688652</v>
+        <v>0.1534675657749176</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.04916061460971832</v>
+        <v>0.1679882407188416</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0378224141895771</v>
+        <v>0.1368544697761536</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.05592629685997963</v>
+        <v>0.1680004745721817</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.008853301405906677</v>
+        <v>0.0809764638543129</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.03975754231214523</v>
+        <v>0.008581414818763733</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.03792041167616844</v>
+        <v>0.08021954447031021</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.01939039677381516</v>
+        <v>0.1161997392773628</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.04301270470023155</v>
+        <v>0.00342490803450346</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.01349073834717274</v>
+        <v>0.07740479707717896</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.003339348360896111</v>
+        <v>0.02624772302806377</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.01569851115345955</v>
+        <v>0.07350236922502518</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.02526458725333214</v>
+        <v>0.04616621881723404</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.02193665504455566</v>
+        <v>0.04112089052796364</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.009015712887048721</v>
+        <v>0.02022089809179306</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.03498371690511703</v>
+        <v>0.0007833447307348251</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.006387430243194103</v>
+        <v>0.001879457384347916</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.01441987603902817</v>
+        <v>0.03516767174005508</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.07194770127534866</v>
+        <v>0.2802457809448242</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.02277873829007149</v>
+        <v>0.03537309542298317</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.02542133815586567</v>
+        <v>0.05655035004019737</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.02423420175909996</v>
+        <v>0.05483917146921158</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.02196370624005795</v>
+        <v>0.08263026922941208</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.01646710745990276</v>
+        <v>0.004680839367210865</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.008209172636270523</v>
+        <v>0.09425012022256851</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.008008105680346489</v>
+        <v>0.07374891638755798</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.009519084356725216</v>
+        <v>0.01357201859354973</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.03556572273373604</v>
+        <v>0.1097274944186211</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.01634428836405277</v>
+        <v>0.04603010788559914</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.01905746012926102</v>
+        <v>0.07605983316898346</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.01002785749733448</v>
+        <v>0.00620035408064723</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.005941075272858143</v>
+        <v>0.001389238983392715</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.008146616630256176</v>
+        <v>0.01138640381395817</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.001082210801541805</v>
+        <v>0.02435978129506111</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.01717848144471645</v>
+        <v>0.01898505911231041</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.05255039036273956</v>
+        <v>0.07022834569215775</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.003211393021047115</v>
+        <v>0.09571553766727448</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.00259664049372077</v>
+        <v>0.02817167341709137</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.06496816128492355</v>
+        <v>0.2159363329410553</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0415484644472599</v>
+        <v>0.1163831129670143</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.006273522973060608</v>
+        <v>0.07706613838672638</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.03060089237987995</v>
+        <v>0.08234459161758423</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.02545219287276268</v>
+        <v>0.02597215212881565</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.0104615893214941</v>
+        <v>0.08123818039894104</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.004224356729537249</v>
+        <v>0.01226825825870037</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.03442685306072235</v>
+        <v>0.1098682060837746</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.02078959159553051</v>
+        <v>0.04377539455890656</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.02705067954957485</v>
+        <v>0.08792203664779663</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.01665511354804039</v>
+        <v>0.01637191325426102</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.008632518351078033</v>
+        <v>0.004503815900534391</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.01152930967509747</v>
+        <v>0.01153840497136116</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.004566405899822712</v>
+        <v>0.02624879963696003</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.01484576240181923</v>
+        <v>0.03001687303185463</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.01378596946597099</v>
+        <v>0.02351256459951401</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.02143139205873013</v>
+        <v>0.1437310874462128</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0320325642824173</v>
+        <v>0.1317615956068039</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.05446454137563705</v>
+        <v>0.05398085713386536</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0274320375174284</v>
+        <v>0.04571152478456497</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.02703686058521271</v>
+        <v>0.1889912188053131</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.02378133311867714</v>
+        <v>0.000272747129201889</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.01857761479914188</v>
+        <v>0.1401969343423843</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.05054804682731628</v>
+        <v>0.03138813376426697</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.007005560211837292</v>
+        <v>0.02369092404842377</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.001714340411126614</v>
+        <v>0.03592830896377563</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.01786784827709198</v>
+        <v>0.007145563140511513</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.02774478495121002</v>
+        <v>0.05299235135316849</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.03500355780124664</v>
+        <v>0.02014134079217911</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.01983479782938957</v>
+        <v>0.02240898460149765</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.002975792158395052</v>
+        <v>0.0120606729760766</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.02841388247907162</v>
+        <v>0.03389203548431396</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.01929978281259537</v>
+        <v>0.1602942943572998</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0007710037752985954</v>
+        <v>0.01273847743868828</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.004806567449122667</v>
+        <v>0.03568021208047867</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.02702200599014759</v>
+        <v>0.05527915805578232</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.01780999079346657</v>
+        <v>0.03514265269041061</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0167417861521244</v>
+        <v>0.08645457774400711</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.002208950463682413</v>
+        <v>0.09663306176662445</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.01046987343579531</v>
+        <v>0.05431370437145233</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0006413921364583075</v>
+        <v>0.1105075925588608</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.01643331907689571</v>
+        <v>0.1038061231374741</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.004532940685749054</v>
+        <v>0.03115886263549328</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.0358881801366806</v>
+        <v>0.07511477172374725</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.02980364859104156</v>
+        <v>0.04012496769428253</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.02018410712480545</v>
+        <v>0.05968445166945457</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.01869592443108559</v>
+        <v>0.02265118435025215</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.01415895018726587</v>
+        <v>0.03623452410101891</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.01597664877772331</v>
+        <v>0.004758390597999096</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.00406309962272644</v>
+        <v>0.007055344991385937</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.009133337065577507</v>
+        <v>0.007143890950828791</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.003669789060950279</v>
+        <v>0.03071631863713264</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.02560064569115639</v>
+        <v>0.1108860597014427</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.03468599170446396</v>
+        <v>0.01573544926941395</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.004859781358391047</v>
+        <v>0.01535823196172714</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.006433809176087379</v>
+        <v>0.0469120517373085</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.01883028447628021</v>
+        <v>0.003068063408136368</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.02345934510231018</v>
+        <v>0.05552602186799049</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.04214225336909294</v>
+        <v>0.04424354061484337</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.001236585900187492</v>
+        <v>0.05372825264930725</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.004425988998264074</v>
+        <v>0.01107644848525524</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.03569778054952621</v>
+        <v>0.1310964524745941</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.01255635917186737</v>
+        <v>0.02119233086705208</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.0200820229947567</v>
+        <v>0.09213943779468536</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.01403935998678207</v>
+        <v>0.01464582979679108</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.008335551247000694</v>
+        <v>0.02135699428617954</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.01060954201966524</v>
+        <v>0.008714213036000729</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.001281492877751589</v>
+        <v>0.02341101132333279</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.02308108285069466</v>
+        <v>0.02825029939413071</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.003563204314559698</v>
+        <v>0.01183893531560898</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.02378027699887753</v>
+        <v>0.06272999197244644</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.02661331929266453</v>
+        <v>0.06774728745222092</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.04469223693013191</v>
+        <v>0.09309718757867813</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.001820793841034174</v>
+        <v>0.01444053277373314</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.0506303608417511</v>
+        <v>0.02299841865897179</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.01213457062840462</v>
+        <v>0.009635647758841515</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.01308829244226217</v>
+        <v>0.009696219116449356</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.03583397716283798</v>
+        <v>0.1209820434451103</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.004111314658075571</v>
+        <v>0.0603531077504158</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.043574508279562</v>
+        <v>0.05602597817778587</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.001429612748324871</v>
+        <v>0.01901590451598167</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.04013138636946678</v>
+        <v>0.008042313158512115</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.004724420607089996</v>
+        <v>0.2885570824146271</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.02230119332671165</v>
+        <v>0.02588294073939323</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.01521024946123362</v>
+        <v>0.05753424018621445</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.00124809518456459</v>
+        <v>0.03517013788223267</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0352819636464119</v>
+        <v>0.1028112396597862</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.06122425943613052</v>
+        <v>0.01344080828130245</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.02357330918312073</v>
+        <v>0.1509962975978851</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.01990619674324989</v>
+        <v>0.05198431760072708</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.01281820237636566</v>
+        <v>0.007884573191404343</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.04651661962270737</v>
+        <v>0.007430564612150192</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.04896027222275734</v>
+        <v>0.01901184394955635</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.06584250926971436</v>
+        <v>0.08977953344583511</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.00769729120656848</v>
+        <v>0.03744059801101685</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.0170406810939312</v>
+        <v>0.004272500984370708</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.03991226106882095</v>
+        <v>0.4258197546005249</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3706024885177612</v>
+        <v>0.9023351669311523</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02701650373637676</v>
+        <v>0.05623544007539749</v>
       </c>
       <c r="D8" t="n">
-        <v>0.202239528298378</v>
+        <v>0.1396838426589966</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04376749321818352</v>
+        <v>0.1556603163480759</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2395875453948975</v>
+        <v>0.3531704545021057</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01195337064564228</v>
+        <v>0.007040627300739288</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08599332720041275</v>
+        <v>0.1128474473953247</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02041669562458992</v>
+        <v>0.1150998771190643</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1018183007836342</v>
+        <v>0.3115746974945068</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2925706207752228</v>
+        <v>1.050435185432434</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005628088489174843</v>
+        <v>0.2192893922328949</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1774495393037796</v>
+        <v>0.4888650476932526</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03161106258630753</v>
+        <v>0.0457267165184021</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2599721252918243</v>
+        <v>0.303447425365448</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0005579981952905655</v>
+        <v>0.06672381609678268</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0009592249989509583</v>
+        <v>0.1271988600492477</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01887878961861134</v>
+        <v>0.08724084496498108</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02593266218900681</v>
+        <v>0.07925780862569809</v>
       </c>
       <c r="T8" t="n">
-        <v>0.04701381921768188</v>
+        <v>0.2555523216724396</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02365004830062389</v>
+        <v>0.0365312471985817</v>
       </c>
       <c r="V8" t="n">
-        <v>0.04322469979524612</v>
+        <v>0.1787308901548386</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02995870262384415</v>
+        <v>0.1315563023090363</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02066626399755478</v>
+        <v>0.03579703718423843</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.04087711498141289</v>
+        <v>0.06093117967247963</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03940816968679428</v>
+        <v>0.2166498452425003</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.04329539090394974</v>
+        <v>0.01609855890274048</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0008783228695392609</v>
+        <v>0.008691877126693726</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.03327227011322975</v>
+        <v>0.1317438930273056</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.01524285133928061</v>
+        <v>0.05299368873238564</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.007474018260836601</v>
+        <v>0.266357958316803</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01568353176116943</v>
+        <v>0.4012899696826935</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.005508884787559509</v>
+        <v>0.1760396361351013</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.01469931751489639</v>
+        <v>0.008618522435426712</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.02575895749032497</v>
+        <v>0.3089357316493988</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0195583701133728</v>
+        <v>0.07031600177288055</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.03145315498113632</v>
+        <v>0.01781067624688148</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.05547257512807846</v>
+        <v>0.2277552038431168</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.01877248659729958</v>
+        <v>0.07254548370838165</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.01129705179482698</v>
+        <v>0.01215476915240288</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.01734653487801552</v>
+        <v>0.1860906183719635</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.04719574749469757</v>
+        <v>0.1581960171461105</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.001254115719348192</v>
+        <v>0.09618636220693588</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.02632728591561317</v>
+        <v>0.3126378953456879</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.05165809392929077</v>
+        <v>0.03201129660010338</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.02326041460037231</v>
+        <v>0.1708794832229614</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.2262705564498901</v>
+        <v>0.9184012413024902</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.01924164034426212</v>
+        <v>0.05944295972585678</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.02583177760243416</v>
+        <v>0.05078979581594467</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.01899210549890995</v>
+        <v>0.1799264401197433</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.128309890627861</v>
+        <v>0.3712015748023987</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.002594396471977234</v>
+        <v>0.02821443043649197</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.05109485611319542</v>
+        <v>0.008044475689530373</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0771840363740921</v>
+        <v>0.02063504979014397</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.05175476521253586</v>
+        <v>0.1343071013689041</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.07257852703332901</v>
+        <v>0.02051715366542339</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.09618771076202393</v>
+        <v>0.03885025531053543</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.05615564063191414</v>
+        <v>0.1731068044900894</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.09094639867544174</v>
+        <v>0.2105225175619125</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.06501796096563339</v>
+        <v>0.1328753232955933</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.01993297785520554</v>
+        <v>0.1211935207247734</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.06352647393941879</v>
+        <v>0.06603477895259857</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0074737798422575</v>
+        <v>0.01188129466027021</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.003175889141857624</v>
+        <v>0.1290425360202789</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.04111801087856293</v>
+        <v>0.02802218124270439</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.04273838922381401</v>
+        <v>0.01742693595588207</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.03848019242286682</v>
+        <v>0.09025560319423676</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.01790172606706619</v>
+        <v>0.07177524268627167</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0002528331242501736</v>
+        <v>0.06598184257745743</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.02249465137720108</v>
+        <v>0.1181540340185165</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.01280170679092407</v>
+        <v>0.05993642285466194</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.008401177823543549</v>
+        <v>0.01957623474299908</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.02087151445448399</v>
+        <v>0.0654652938246727</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1199531331658363</v>
+        <v>0.6893845796585083</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.0506792888045311</v>
+        <v>0.05199333280324936</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.05466004088521004</v>
+        <v>0.147413969039917</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.03219272941350937</v>
+        <v>0.06951054930686951</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.04330921173095703</v>
+        <v>0.2241940945386887</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.02238618955016136</v>
+        <v>0.1081749647855759</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0252255629748106</v>
+        <v>0.1144343018531799</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0588139072060585</v>
+        <v>0.03416979685425758</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.004201129544526339</v>
+        <v>0.07693568617105484</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.05838032811880112</v>
+        <v>0.2811120748519897</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0481085330247879</v>
+        <v>0.02246138826012611</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.03193579241633415</v>
+        <v>0.08561963587999344</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.02279194630682468</v>
+        <v>0.03280428051948547</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.04277700558304787</v>
+        <v>0.1285695433616638</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.01862684637308121</v>
+        <v>0.06157472357153893</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0138963982462883</v>
+        <v>0.003141073044389486</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.03242474794387817</v>
+        <v>0.03918752074241638</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.04160402342677116</v>
+        <v>0.1970825344324112</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.001566749997437</v>
+        <v>0.5924739837646484</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.01918019354343414</v>
+        <v>0.08403091877698898</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.03264216706156731</v>
+        <v>0.2137776613235474</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.002481010276824236</v>
+        <v>0.311339259147644</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.004041394218802452</v>
+        <v>0.3759855628013611</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.05626946687698364</v>
+        <v>0.0267648920416832</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.05307390540838242</v>
+        <v>0.03212655335664749</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.005839315243065357</v>
+        <v>0.06052964925765991</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.002136111259460449</v>
+        <v>0.02189989015460014</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.05319245532155037</v>
+        <v>0.2683233618736267</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.04584384709596634</v>
+        <v>0.01375798135995865</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.04840312525629997</v>
+        <v>0.06655234843492508</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.02160840667784214</v>
+        <v>0.06767573952674866</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.04814815521240234</v>
+        <v>0.107914000749588</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.01687032356858253</v>
+        <v>0.01133218593895435</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.03408180922269821</v>
+        <v>0.007815784774720669</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.02063731849193573</v>
+        <v>0.06963907182216644</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.02404263243079185</v>
+        <v>0.3249564468860626</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.04454940930008888</v>
+        <v>0.0830022320151329</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.01447658613324165</v>
+        <v>0.02898854203522205</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.1158683300018311</v>
+        <v>0.0950821191072464</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.003284525126218796</v>
+        <v>0.2547134757041931</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0009193895384669304</v>
+        <v>0.02282979153096676</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.03743554279208183</v>
+        <v>0.1194806694984436</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.04055200889706612</v>
+        <v>0.03797554969787598</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.01356407441198826</v>
+        <v>0.1514948904514313</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.004813277162611485</v>
+        <v>0.0429326556622982</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.005301191471517086</v>
+        <v>0.1184338629245758</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.02750195376574993</v>
+        <v>0.07578770071268082</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.02636831812560558</v>
+        <v>0.1477433294057846</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01342723798006773</v>
+        <v>0.01545425131917</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.008744715712964535</v>
+        <v>0.02022744342684746</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.02255991660058498</v>
+        <v>0.02315489202737808</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.004054966382682323</v>
+        <v>0.2343268245458603</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.05637132003903389</v>
+        <v>0.02672695182263851</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.01519791223108768</v>
+        <v>0.1081312224268913</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.02501221373677254</v>
+        <v>0.1677889227867126</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.05863742902874947</v>
+        <v>0.133864089846611</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.001923093572258949</v>
+        <v>0.03155148029327393</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.003962449263781309</v>
+        <v>0.07168792933225632</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.02739131823182106</v>
+        <v>0.1313007473945618</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.004671803675591946</v>
+        <v>0.0340438038110733</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.02357520721852779</v>
+        <v>0.04723820462822914</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.003307790495455265</v>
+        <v>0.1945293098688126</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.02122171968221664</v>
+        <v>0.09283749759197235</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.04540328681468964</v>
+        <v>0.03138256818056107</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0351250134408474</v>
+        <v>0.01528745703399181</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.00209565949626267</v>
+        <v>0.01039074547588825</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.001370293088257313</v>
+        <v>0.1575344949960709</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.04066507145762444</v>
+        <v>0.02131987921893597</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.0231635682284832</v>
+        <v>0.02556241676211357</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.003530331421643496</v>
+        <v>0.04868179932236671</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.01012960821390152</v>
+        <v>0.04657582938671112</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.001999790780246258</v>
+        <v>0.005682751536369324</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.02505683153867722</v>
+        <v>0.09740478545427322</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.05208823829889297</v>
+        <v>0.02675782516598701</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.03242974355816841</v>
+        <v>0.1212094873189926</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.02897092327475548</v>
+        <v>0.2948703169822693</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.04764899238944054</v>
+        <v>0.07500834763050079</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.04193613305687904</v>
+        <v>0.03870027512311935</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.06417530030012131</v>
+        <v>0.050161212682724</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.001712617930024862</v>
+        <v>0.04265765845775604</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.004832574166357517</v>
+        <v>0.05714815109968185</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.05147995054721832</v>
+        <v>0.3147546648979187</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.03694120049476624</v>
+        <v>0.01997195370495319</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.0401843897998333</v>
+        <v>0.08336049318313599</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.02724707499146461</v>
+        <v>0.08294349908828735</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.03847162798047066</v>
+        <v>0.1222810000181198</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.03166303783655167</v>
+        <v>0.07609317451715469</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.02063711360096931</v>
+        <v>0.008400999940931797</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.03405648469924927</v>
+        <v>0.07715507596731186</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.01327623706310987</v>
+        <v>0.05043642222881317</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.02620340511202812</v>
+        <v>0.241739496588707</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.04650428146123886</v>
+        <v>0.009282715618610382</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.05211788415908813</v>
+        <v>0.2300196886062622</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.009885628707706928</v>
+        <v>0.1427125930786133</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.02980052120983601</v>
+        <v>0.1081963032484055</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.01638757064938545</v>
+        <v>0.1235154122114182</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.02127730287611485</v>
+        <v>0.301606148481369</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.02419129014015198</v>
+        <v>0.02833708003163338</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.01268060691654682</v>
+        <v>0.3664956390857697</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.0690118595957756</v>
+        <v>0.5667105317115784</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.03772319480776787</v>
+        <v>0.1150221824645996</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.0623323954641819</v>
+        <v>0.3670486807823181</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.0407879538834095</v>
+        <v>0.1178296878933907</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.02127711102366447</v>
+        <v>0.1755116134881973</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.0278327502310276</v>
+        <v>0.1063807308673859</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.02071288600564003</v>
+        <v>0.02076372876763344</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.00819749478250742</v>
+        <v>0.1032687872648239</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.06995092332363129</v>
+        <v>0.1235321462154388</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.009982540272176266</v>
+        <v>0.08498466014862061</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.01176863070577383</v>
+        <v>0.05253434926271439</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.01460978947579861</v>
+        <v>0.2725341022014618</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.03535868600010872</v>
+        <v>0.07097619771957397</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.03355983272194862</v>
+        <v>0.1319779008626938</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.1722525358200073</v>
+        <v>0.04567090421915054</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.002062737010419369</v>
+        <v>0.04363836348056793</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.02877094224095345</v>
+        <v>0.1306067407131195</v>
       </c>
     </row>
     <row r="9">
@@ -5551,2278 +5551,2278 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.03012226894497871</v>
+        <v>1.896592220873572e-05</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1127201467752457</v>
+        <v>7.287690095836297e-05</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01309815887361765</v>
+        <v>6.226497589523206e-06</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03411699086427689</v>
+        <v>2.265433431603014e-05</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06488474458456039</v>
+        <v>7.827444278518669e-06</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0009741795947775245</v>
+        <v>1.694074308034033e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0152397071942687</v>
+        <v>5.602032160823001e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00941069982945919</v>
+        <v>5.699667781300377e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0004644939326681197</v>
+        <v>1.761624844220933e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01885955221951008</v>
+        <v>2.92752702080179e-08</v>
       </c>
       <c r="K10" t="n">
-        <v>0.07587766647338867</v>
+        <v>7.994018233148381e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008774781599640846</v>
+        <v>2.53789289672568e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03569138795137405</v>
+        <v>4.11307264585048e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.06541205942630768</v>
+        <v>3.457703132880852e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01759296841919422</v>
+        <v>2.182721436838619e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005200177896767855</v>
+        <v>2.007980583584867e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.04712911322712898</v>
+        <v>2.510091871954501e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01070365868508816</v>
+        <v>2.820926965796389e-06</v>
       </c>
       <c r="S10" t="n">
-        <v>0.004100442864000797</v>
+        <v>8.677338882989716e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.03734380006790161</v>
+        <v>2.69163374468917e-05</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0008455818751826882</v>
+        <v>9.585761290509254e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01003280002623796</v>
+        <v>1.126768711401382e-05</v>
       </c>
       <c r="W10" t="n">
-        <v>0.006018416490405798</v>
+        <v>1.415691804140806e-05</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0184665136039257</v>
+        <v>4.174215519014979e-06</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01737495325505733</v>
+        <v>4.676890966948122e-06</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.006663111969828606</v>
+        <v>9.721838068799116e-06</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.008187473751604557</v>
+        <v>7.159114375099307e-06</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.009336767718195915</v>
+        <v>7.869071851018816e-06</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.02463779412209988</v>
+        <v>6.165500963106751e-06</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.006604806054383516</v>
+        <v>1.000437714537838e-05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.01487496122717857</v>
+        <v>2.53546386375092e-05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.02373581565916538</v>
+        <v>3.374003790668212e-05</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.003501428756862879</v>
+        <v>3.989968718087766e-06</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.02336747385561466</v>
+        <v>1.659044528423692e-06</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.007786132395267487</v>
+        <v>7.612181889271596e-06</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.00102467299439013</v>
+        <v>2.510351350792916e-06</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.02057413198053837</v>
+        <v>3.896413545589894e-06</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.02246604487299919</v>
+        <v>2.006542854360305e-05</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.006645209155976772</v>
+        <v>1.032339469020371e-06</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.00749669736251235</v>
+        <v>1.493649506301153e-07</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.01146626751869917</v>
+        <v>2.544953531469218e-06</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.005545609164983034</v>
+        <v>3.370411377545679e-06</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.005425998941063881</v>
+        <v>2.273071913805325e-06</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0007611621404066682</v>
+        <v>4.259365141479066e-06</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.00886126421391964</v>
+        <v>5.804767170047853e-06</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.02596181631088257</v>
+        <v>2.11665633287339e-06</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.1191767528653145</v>
+        <v>6.284566188696772e-05</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.009837997145950794</v>
+        <v>6.004840997775318e-06</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.006768081337213516</v>
+        <v>8.525192242814228e-06</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.01149281207472086</v>
+        <v>2.289198710059281e-05</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.006039295345544815</v>
+        <v>1.810833509807708e-06</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.001578187220729887</v>
+        <v>9.833556759986095e-07</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.02084985561668873</v>
+        <v>1.011586482491111e-05</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.001528106280602515</v>
+        <v>5.236003744357731e-06</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.01530642993748188</v>
+        <v>2.211430546594784e-05</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0161961130797863</v>
+        <v>4.043522949359613e-06</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.02043894305825233</v>
+        <v>1.01137020465103e-05</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.01410460472106934</v>
+        <v>1.962205169547815e-05</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.03804534301161766</v>
+        <v>2.453810884617269e-05</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.01411006599664688</v>
+        <v>3.191780706401914e-06</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.00867030955851078</v>
+        <v>9.640345524530858e-06</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.03815451264381409</v>
+        <v>8.561144568375312e-06</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.005273159127682447</v>
+        <v>1.164658897323534e-05</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.01054221019148827</v>
+        <v>6.061668045731494e-06</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.05035394430160522</v>
+        <v>4.245690433890559e-06</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.0005987392505630851</v>
+        <v>1.017254135149415e-06</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.04058598354458809</v>
+        <v>2.948253722934169e-06</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.04122669622302055</v>
+        <v>2.53228354267776e-05</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.02515665628015995</v>
+        <v>1.340533071925165e-05</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0009515786077827215</v>
+        <v>1.034669548971578e-05</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.01472888607531786</v>
+        <v>1.739343133522198e-06</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.002484069671481848</v>
+        <v>1.218545321535203e-06</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.0136821623891592</v>
+        <v>2.033693453995511e-05</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.06504732370376587</v>
+        <v>5.380151560530066e-05</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.01987243443727493</v>
+        <v>5.143789621797623e-06</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.005665312521159649</v>
+        <v>9.69405664363876e-06</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.008791366592049599</v>
+        <v>5.360535396903288e-06</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.01519888918846846</v>
+        <v>9.226301699527539e-06</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.02958579361438751</v>
+        <v>1.98125007955241e-06</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.01177760120481253</v>
+        <v>1.238368076883489e-05</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.005189631134271622</v>
+        <v>5.548145054490305e-09</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0002012511249631643</v>
+        <v>4.798917871084996e-06</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.01947463303804398</v>
+        <v>1.768626134435181e-05</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.002907294547185302</v>
+        <v>5.381791197578423e-06</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.01591075398027897</v>
+        <v>8.067977432801854e-07</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.005248608067631721</v>
+        <v>5.275157491269056e-06</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.008956183679401875</v>
+        <v>8.780341886449605e-06</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.001440385822206736</v>
+        <v>6.087034307711292e-07</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0008005464333109558</v>
+        <v>2.915183131335652e-06</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.008278383873403072</v>
+        <v>3.357486548338784e-06</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.04888058081269264</v>
+        <v>1.053377400239697e-05</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.04405476525425911</v>
+        <v>2.721192686294671e-05</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.0001472972799092531</v>
+        <v>9.28458302951185e-06</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.0158014353364706</v>
+        <v>8.984468877315521e-06</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.04242601990699768</v>
+        <v>3.879474388668314e-05</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.002559418557211757</v>
+        <v>7.164631824707612e-06</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.007823220454156399</v>
+        <v>8.389974937017541e-06</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.00653317105025053</v>
+        <v>2.012143340834882e-06</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.004790373612195253</v>
+        <v>2.693838951017824e-06</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.001873097382485867</v>
+        <v>8.565771167923231e-07</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.0137105779722333</v>
+        <v>1.735932346491609e-05</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.005871762987226248</v>
+        <v>5.320030595612479e-06</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.02330190129578114</v>
+        <v>9.136972494161455e-07</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.001887722522951663</v>
+        <v>6.070531981094973e-06</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.01109820883721113</v>
+        <v>6.660955477855168e-06</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.001636782428249717</v>
+        <v>2.153471768906456e-06</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.004660897422581911</v>
+        <v>5.702904218196636e-06</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.004611452575773001</v>
+        <v>3.306540747871622e-06</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.03816147148609161</v>
+        <v>2.051984301942866e-05</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.06083832308650017</v>
+        <v>5.491970114235301e-06</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.000184128963155672</v>
+        <v>1.79312360160111e-06</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.06554004549980164</v>
+        <v>8.438742952421308e-06</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.01702569983899593</v>
+        <v>7.002768143138383e-07</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.002544652204960585</v>
+        <v>2.311416028533131e-05</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.05784507840871811</v>
+        <v>9.671281986811664e-06</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.02233752980828285</v>
+        <v>1.005109652396641e-06</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.003266755491495132</v>
+        <v>3.619922790676355e-05</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.02136010862886906</v>
+        <v>6.444627160817618e-06</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.01633279025554657</v>
+        <v>1.33801695483271e-05</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.002222702139988542</v>
+        <v>3.743133220268646e-06</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.008379205130040646</v>
+        <v>1.489576789026614e-06</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.01875111274421215</v>
+        <v>1.210078517033253e-05</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.006405366584658623</v>
+        <v>1.572547989781015e-05</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.008574587292969227</v>
+        <v>1.455254960092134e-06</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.01103715319186449</v>
+        <v>8.173081369022839e-06</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.009693802334368229</v>
+        <v>2.215682343376102e-06</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.01039280463010073</v>
+        <v>1.098115444619907e-05</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.003474750090390444</v>
+        <v>2.138084164471366e-05</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.01072608586400747</v>
+        <v>5.868113476026338e-06</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.02983425557613373</v>
+        <v>2.896014393627411e-06</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.02144984900951385</v>
+        <v>2.477012822055258e-05</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.01041110046207905</v>
+        <v>7.71920895203948e-06</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0177021250128746</v>
+        <v>2.021445652644616e-06</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.00463855592533946</v>
+        <v>1.199349571834318e-05</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.003545802086591721</v>
+        <v>4.583086138154613e-06</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.01291697844862938</v>
+        <v>3.011673925357172e-06</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.0004152039182372391</v>
+        <v>2.632992163853487e-06</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.001052795676514506</v>
+        <v>3.582229055609787e-06</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.03692987188696861</v>
+        <v>3.971986188844312e-06</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.01901019550859928</v>
+        <v>2.439146101096412e-06</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.01008601300418377</v>
+        <v>9.378061804454774e-06</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.006903310306370258</v>
+        <v>3.488130005280254e-06</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.003873540554195642</v>
+        <v>5.873687769053504e-06</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.001177754136733711</v>
+        <v>4.421552148414776e-06</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.01753291115164757</v>
+        <v>1.724982780615392e-06</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.003234361531212926</v>
+        <v>6.687551831419114e-06</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.01736916042864323</v>
+        <v>9.293964922107989e-07</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.01722421124577522</v>
+        <v>5.036494712840067e-06</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.006564878858625889</v>
+        <v>1.298194274568232e-05</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.01768003217875957</v>
+        <v>7.826471119187772e-06</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.004956093151122332</v>
+        <v>3.416910203668522e-06</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.009670021012425423</v>
+        <v>5.599377345788525e-06</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.006460039876401424</v>
+        <v>6.838145054643974e-06</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0003136568702757359</v>
+        <v>3.557611989890574e-06</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.01089922524988651</v>
+        <v>1.935762884386349e-05</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.002704053418710828</v>
+        <v>3.938411737181013e-06</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.01864333637058735</v>
+        <v>3.865807229885831e-08</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.001678014872595668</v>
+        <v>4.884295776719227e-07</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.01119199674576521</v>
+        <v>6.972506071178941e-06</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.004232757724821568</v>
+        <v>3.38634777108382e-07</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.002907342044636607</v>
+        <v>6.383188519976102e-06</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.007731154095381498</v>
+        <v>8.50035939947702e-06</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.01506997644901276</v>
+        <v>8.657762009534054e-06</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.02001497335731983</v>
+        <v>1.642936808821105e-06</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.01427080202847719</v>
+        <v>1.942661128850887e-06</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.003713356563821435</v>
+        <v>6.063149157853331e-06</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.00957846362143755</v>
+        <v>1.594587774889078e-05</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.008088047616183758</v>
+        <v>3.244748086217442e-06</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.005733831319957972</v>
+        <v>9.446270610169449e-07</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.00503899110481143</v>
+        <v>1.209458423545584e-05</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.003054639557376504</v>
+        <v>4.626408099284163e-06</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.01147746481001377</v>
+        <v>1.102186706702923e-05</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.003105501877143979</v>
+        <v>2.972464244521689e-05</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.0134167680516839</v>
+        <v>1.325385164818726e-05</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.03842197358608246</v>
+        <v>1.898781192721799e-05</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.02485858462750912</v>
+        <v>4.184486897429451e-05</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.007700713351368904</v>
+        <v>2.59467833529925e-06</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.009126899763941765</v>
+        <v>7.258825462486129e-06</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.02907511219382286</v>
+        <v>6.933411441423232e-06</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0001408324460498989</v>
+        <v>5.255999894870911e-06</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.01791926100850105</v>
+        <v>1.680677996773738e-05</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.02982952445745468</v>
+        <v>1.900764618767425e-05</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.01150678843259811</v>
+        <v>1.348929799860343e-05</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.01661542803049088</v>
+        <v>1.558598160045221e-05</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.003354147309437394</v>
+        <v>2.997769843204878e-05</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.01694303750991821</v>
+        <v>4.883540441369405e-06</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.03342152759432793</v>
+        <v>4.202680429443717e-06</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.02571737021207809</v>
+        <v>7.488873052352574e-06</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0007841588230803609</v>
+        <v>2.059209691651631e-08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.02759500779211521</v>
+        <v>0.03350371867418289</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1859644800424576</v>
+        <v>0.08692052960395813</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00749886641278863</v>
+        <v>0.02529515512287617</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04449662938714027</v>
+        <v>0.01246881671249866</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01928612031042576</v>
+        <v>0.02891015447676182</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03512324392795563</v>
+        <v>0.001406343537382782</v>
       </c>
       <c r="G11" t="n">
-        <v>0.008753789588809013</v>
+        <v>0.007700466085225344</v>
       </c>
       <c r="H11" t="n">
-        <v>0.005112582817673683</v>
+        <v>0.00730116106569767</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02395706064999104</v>
+        <v>0.01825784705579281</v>
       </c>
       <c r="J11" t="n">
-        <v>0.03870249912142754</v>
+        <v>0.02259613201022148</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1404530853033066</v>
+        <v>0.1179752945899963</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0004947693669237196</v>
+        <v>0.02460349351167679</v>
       </c>
       <c r="M11" t="n">
-        <v>0.03997950255870819</v>
+        <v>0.02916271239519119</v>
       </c>
       <c r="N11" t="n">
-        <v>0.03680889308452606</v>
+        <v>0.03301700204610825</v>
       </c>
       <c r="O11" t="n">
-        <v>0.03618716821074486</v>
+        <v>0.02181488461792469</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01385861821472645</v>
+        <v>0.003532967064529657</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01522425934672356</v>
+        <v>0.02300769090652466</v>
       </c>
       <c r="R11" t="n">
-        <v>0.03079834207892418</v>
+        <v>0.0252121165394783</v>
       </c>
       <c r="S11" t="n">
-        <v>0.006353600881993771</v>
+        <v>0.003849288448691368</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03755853697657585</v>
+        <v>0.01247872691601515</v>
       </c>
       <c r="U11" t="n">
-        <v>0.004041987471282482</v>
+        <v>0.008299372158944607</v>
       </c>
       <c r="V11" t="n">
-        <v>0.02313247323036194</v>
+        <v>0.01044980436563492</v>
       </c>
       <c r="W11" t="n">
-        <v>0.004878943786025047</v>
+        <v>0.003817783202975988</v>
       </c>
       <c r="X11" t="n">
-        <v>0.02870947867631912</v>
+        <v>0.01241990830749273</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.007073147222399712</v>
+        <v>0.0006723030237480998</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.02499787695705891</v>
+        <v>0.009931047447025776</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01303263008594513</v>
+        <v>0.01505808997899294</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.002514350228011608</v>
+        <v>0.003580485237762332</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.02532180398702621</v>
+        <v>0.001968211960047483</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.00993555411696434</v>
+        <v>0.01283397059887648</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.005249709822237492</v>
+        <v>0.01303447689861059</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.02605257742106915</v>
+        <v>0.01558027602732182</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.03654049336910248</v>
+        <v>0.01342874206602573</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.008468920364975929</v>
+        <v>0.006513840518891811</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.003257366362959146</v>
+        <v>0.0229252427816391</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.01091800164431334</v>
+        <v>0.01070100720971823</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.01853809878230095</v>
+        <v>0.003748030168935657</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03286920487880707</v>
+        <v>0.02860770560801029</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.004945769906044006</v>
+        <v>0.001961566507816315</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.01390007883310318</v>
+        <v>0.009912174195051193</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.008202215656638145</v>
+        <v>0.008495503105223179</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.02588010206818581</v>
+        <v>0.0005614449619315565</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.01047411467880011</v>
+        <v>0.006569082848727703</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.005938308779150248</v>
+        <v>0.01891326159238815</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0152928251773119</v>
+        <v>0.002999150427058339</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.004779733717441559</v>
+        <v>0.004332141485065222</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1073350980877876</v>
+        <v>0.08701395243406296</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.006326788570731878</v>
+        <v>0.01118394546210766</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.01318204030394554</v>
+        <v>0.01141401566565037</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.01092442683875561</v>
+        <v>0.01176818832755089</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.02060450613498688</v>
+        <v>0.003221711842343211</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.008937926962971687</v>
+        <v>0.001893718144856393</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.007820823229849339</v>
+        <v>0.002899452578276396</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.005490421317517757</v>
+        <v>0.002510538091883063</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.005063532385975122</v>
+        <v>0.02394691482186317</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.03391365706920624</v>
+        <v>0.01660884357988834</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.01417379081249237</v>
+        <v>0.02317547053098679</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.002233723178505898</v>
+        <v>0.004549860022962093</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.03048870526254177</v>
+        <v>0.03078318387269974</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.004112933296710253</v>
+        <v>0.00453238608315587</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.01275850087404251</v>
+        <v>0.004954364150762558</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.01423207577317953</v>
+        <v>0.01214320678263903</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.02416597120463848</v>
+        <v>0.006106133107095957</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.003713428508490324</v>
+        <v>0.002798510249704123</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.01395357586443424</v>
+        <v>0.01337136793881655</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.003375293454155326</v>
+        <v>0.005108837969601154</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.0131174698472023</v>
+        <v>0.001943459501489997</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.02907210402190685</v>
+        <v>0.008492461405694485</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.02110854908823967</v>
+        <v>0.006358035374432802</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.005870943889021873</v>
+        <v>0.02302295528352261</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.009965335018932819</v>
+        <v>0.000280859210761264</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.02167515084147453</v>
+        <v>0.008587440475821495</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.007178491912782192</v>
+        <v>0.008088326081633568</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.07475323975086212</v>
+        <v>0.07305066287517548</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.01910967938601971</v>
+        <v>0.005478124599903822</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.02481677383184433</v>
+        <v>0.01196642033755779</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.001514715724624693</v>
+        <v>0.000365198589861393</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.001116340165026486</v>
+        <v>0.003430723212659359</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.005287920124828815</v>
+        <v>0.0147660356014967</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.01112877018749714</v>
+        <v>0.002829384058713913</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.01114058867096901</v>
+        <v>0.01250486820936203</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.005550763569772243</v>
+        <v>0.006367399357259274</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.02743666060268879</v>
+        <v>0.03163739666342735</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.006535694003105164</v>
+        <v>0.007918891496956348</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.006687214132398367</v>
+        <v>2.230261452496052e-05</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.004480481147766113</v>
+        <v>0.0003799616824835539</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.002646669978275895</v>
+        <v>0.008465521968901157</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.002543216804042459</v>
+        <v>0.002158047631382942</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.00535071874037385</v>
+        <v>0.00538615882396698</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.002220041584223509</v>
+        <v>0.004993136506527662</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.02975256368517876</v>
+        <v>0.01204816251993179</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.005728339776396751</v>
+        <v>0.06411528587341309</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.948638237081468e-05</v>
+        <v>0.002584242727607489</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.01024437230080366</v>
+        <v>0.009435690939426422</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.0390520803630352</v>
+        <v>0.007289298344403505</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.005561215803027153</v>
+        <v>0.01131800189614296</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.01352506782859564</v>
+        <v>0.009674057364463806</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.01454662438482046</v>
+        <v>0.0233243890106678</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.01216002646833658</v>
+        <v>0.001061251037754118</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.002476117108017206</v>
+        <v>0.003686745651066303</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.02834261208772659</v>
+        <v>0.03231343999505043</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.008946609683334827</v>
+        <v>0.007695822510868311</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.01070425845682621</v>
+        <v>0.003366109915077686</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.006517460569739342</v>
+        <v>0.002570946700870991</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.01175716798752546</v>
+        <v>0.007435677573084831</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.005391097627580166</v>
+        <v>0.0001225677551701665</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.006095162127166986</v>
+        <v>0.005669757723808289</v>
       </c>
       <c r="DD11" t="n">
-        <v>5.052174310549162e-05</v>
+        <v>0.009704142808914185</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.0016603316180408</v>
+        <v>0.01006386801600456</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.0641840472817421</v>
+        <v>0.04375177621841431</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.0002192731772083789</v>
+        <v>0.01052847318351269</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.03597969561815262</v>
+        <v>0.01466293446719646</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01654715090990067</v>
+        <v>0.007030797190964222</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.04237109050154686</v>
+        <v>0.03851111233234406</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.0005799736827611923</v>
+        <v>0.003830407280474901</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.0004606416914612055</v>
+        <v>0.0009751489269547164</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.01596053689718246</v>
+        <v>0.003711657132953405</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.00360245443880558</v>
+        <v>0.001679736888036132</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.0214561503380537</v>
+        <v>0.01537454035133123</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.00227212649770081</v>
+        <v>0.01413428224623203</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.01106477156281471</v>
+        <v>0.009989287704229355</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.02263367921113968</v>
+        <v>0.001675630453974009</v>
       </c>
       <c r="DS11" t="n">
-        <v>9.504245826974511e-05</v>
+        <v>0.008189531043171883</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.003221204970031977</v>
+        <v>0.0003481485182419419</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.00297012971714139</v>
+        <v>0.01196719706058502</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.02145582064986229</v>
+        <v>0.01254996284842491</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.001634169835597277</v>
+        <v>0.01070366241037846</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0202200822532177</v>
+        <v>0.016974788159132</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.01115433964878321</v>
+        <v>0.005412496626377106</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.008524668402969837</v>
+        <v>0.007249798160046339</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.01817566715180874</v>
+        <v>0.005887663457542658</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0103760315105319</v>
+        <v>0.02552642486989498</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.006167850457131863</v>
+        <v>0.002007748931646347</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.005798204801976681</v>
+        <v>0.01414436008781195</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.01065713725984097</v>
+        <v>0.0178067684173584</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.003766049165278673</v>
+        <v>0.00250193290412426</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.00702327536419034</v>
+        <v>0.01642365008592606</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.006826406810432673</v>
+        <v>0.003083787858486176</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.008272828534245491</v>
+        <v>0.001855220180004835</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.003064665710553527</v>
+        <v>0.004567616153508425</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.01596767269074917</v>
+        <v>0.007581085897982121</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.004874794743955135</v>
+        <v>0.00064842589199543</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.001265312545001507</v>
+        <v>0.009821691550314426</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.003339379793033004</v>
+        <v>0.001667619915679097</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.003515642136335373</v>
+        <v>0.001140848267823458</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01396780461072922</v>
+        <v>0.02065218240022659</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.01210260670632124</v>
+        <v>0.002463215496391058</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.008178792893886566</v>
+        <v>0.005945386365056038</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.005266303662210703</v>
+        <v>0.004041227046400309</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.01994788087904453</v>
+        <v>0.008836135268211365</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.00803699903190136</v>
+        <v>0.004825717769563198</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.02357137016952038</v>
+        <v>0.001892421976663172</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.004906383343040943</v>
+        <v>0.00248589483089745</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.002352225128561258</v>
+        <v>0.004919754806905985</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.02868761122226715</v>
+        <v>0.03793365508317947</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.004739769268780947</v>
+        <v>0.00810551643371582</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.01115298178046942</v>
+        <v>0.001745000015944242</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01033898629248142</v>
+        <v>0.001394976512528956</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.009045633487403393</v>
+        <v>0.007982227951288223</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.003791367402300239</v>
+        <v>0.002350121038034558</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.001382210059091449</v>
+        <v>0.004367145709693432</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.004008709453046322</v>
+        <v>0.009867810644209385</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.0001315540866926312</v>
+        <v>0.003300843061879277</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.01029986888170242</v>
+        <v>0.01347511447966099</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.007897324860095978</v>
+        <v>0.01519855670630932</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.005988847464323044</v>
+        <v>0.01137100905179977</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.007378980983048677</v>
+        <v>0.004102122504264116</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.003042571945115924</v>
+        <v>0.004287493415176868</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.004415177740156651</v>
+        <v>0.008640794083476067</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.004757349845021963</v>
+        <v>0.003643082454800606</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.004605380352586508</v>
+        <v>0.01552491821348667</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.008689001202583313</v>
+        <v>0.01010856591165066</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.02244426868855953</v>
+        <v>0.01068936567753553</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.01368111651390791</v>
+        <v>0.003158073406666517</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.02611268498003483</v>
+        <v>0.008326591923832893</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0002444530837237835</v>
+        <v>0.02984597720205784</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.003290965687483549</v>
+        <v>0.008883136324584484</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.01476482022553682</v>
+        <v>0.003700256813317537</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.004900000058114529</v>
+        <v>0.02133573964238167</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.01127923186868429</v>
+        <v>0.02370739355683327</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.01965648122131824</v>
+        <v>0.0003219498321413994</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.004976620431989431</v>
+        <v>0.0205703042447567</v>
       </c>
       <c r="GA11" t="n">
-        <v>6.151199340820312e-05</v>
+        <v>0.009788551367819309</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.01113398745656013</v>
+        <v>0.001258269650861621</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.06983210891485214</v>
+        <v>0.006841729395091534</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.02699921652674675</v>
+        <v>0.001141481101512909</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.05434849113225937</v>
+        <v>0.007021138910204172</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.003333470318466425</v>
+        <v>0.01036304701119661</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.008275385014712811</v>
+        <v>0.01259035244584084</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.001567959319800138</v>
+        <v>0.009072554297745228</v>
       </c>
       <c r="B12" t="n">
-        <v>0.08620385080575943</v>
+        <v>0.01574428379535675</v>
       </c>
       <c r="C12" t="n">
-        <v>0.004370290320366621</v>
+        <v>0.002484457567334175</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01488096546381712</v>
+        <v>0.006806313991546631</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02239872701466084</v>
+        <v>0.01493368111550808</v>
       </c>
       <c r="F12" t="n">
-        <v>0.009369951672852039</v>
+        <v>0.004703161772340536</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0531504787504673</v>
+        <v>0.008878879249095917</v>
       </c>
       <c r="H12" t="n">
-        <v>0.001076655695214868</v>
+        <v>0.005830745678395033</v>
       </c>
       <c r="I12" t="n">
-        <v>0.007556445896625519</v>
+        <v>0.00772442203015089</v>
       </c>
       <c r="J12" t="n">
-        <v>0.008329928852617741</v>
+        <v>0.006096024997532368</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06257939338684082</v>
+        <v>0.02374194748699665</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001179769751615822</v>
+        <v>0.006696993485093117</v>
       </c>
       <c r="M12" t="n">
-        <v>0.03880654275417328</v>
+        <v>0.009070530533790588</v>
       </c>
       <c r="N12" t="n">
-        <v>0.02993777021765709</v>
+        <v>0.01367222331464291</v>
       </c>
       <c r="O12" t="n">
-        <v>0.000189648853847757</v>
+        <v>0.003760689403861761</v>
       </c>
       <c r="P12" t="n">
-        <v>0.04344216734170914</v>
+        <v>0.0139416391029954</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.01438582688570023</v>
+        <v>0.008302279748022556</v>
       </c>
       <c r="R12" t="n">
-        <v>0.000872518983669579</v>
+        <v>0.003300782293081284</v>
       </c>
       <c r="S12" t="n">
-        <v>0.008687444962561131</v>
+        <v>0.004284900147467852</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02194667048752308</v>
+        <v>0.0005662781186401844</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0008919193642213941</v>
+        <v>0.0009168750839307904</v>
       </c>
       <c r="V12" t="n">
-        <v>0.005059428513050079</v>
+        <v>0.0004336012934800237</v>
       </c>
       <c r="W12" t="n">
-        <v>0.01507317554205656</v>
+        <v>0.003402518574148417</v>
       </c>
       <c r="X12" t="n">
-        <v>0.009932934306561947</v>
+        <v>0.004087896086275578</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.007387509103864431</v>
+        <v>0.003035608446225524</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.002202012343332171</v>
+        <v>0.002723437966778874</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.002088624751195312</v>
+        <v>5.321108983480372e-05</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.009718630462884903</v>
+        <v>0.008769942447543144</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.01835432089865208</v>
+        <v>0.00272905477322638</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.001210856251418591</v>
+        <v>0.008363077417016029</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.006569130346179008</v>
+        <v>0.002525610849261284</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.00532505102455616</v>
+        <v>0.006797772832214832</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.005609828978776932</v>
+        <v>0.002611601259559393</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.006601780187338591</v>
+        <v>0.002252104924991727</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.007841357961297035</v>
+        <v>0.001891228137537837</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.009149838238954544</v>
+        <v>0.000827938609290868</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.008197177201509476</v>
+        <v>0.00373013224452734</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.01001793425530195</v>
+        <v>0.006423220504075289</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.003851498011499643</v>
+        <v>2.994252645294182e-05</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.01193287316709757</v>
+        <v>0.0005747152026742697</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0003376951208338141</v>
+        <v>0.0007923184894025326</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.003737223101779819</v>
+        <v>0.002505782060325146</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.004943251609802246</v>
+        <v>0.0006764093413949013</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.001900247531011701</v>
+        <v>0.0009788078023120761</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.002095025265589356</v>
+        <v>0.002223045099526644</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.01321063004434109</v>
+        <v>0.004640230908989906</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.06607993692159653</v>
+        <v>0.02166744880378246</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.008731197565793991</v>
+        <v>0.006489753257483244</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.01774667203426361</v>
+        <v>0.003321394324302673</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.003981067799031734</v>
+        <v>0.0004751712549477816</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.003461237298324704</v>
+        <v>0.002629127819091082</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.01316122990101576</v>
+        <v>0.001817047595977783</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.009618187323212624</v>
+        <v>0.006362329702824354</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.0005588107160292566</v>
+        <v>8.931232150644064e-05</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.001631982624530792</v>
+        <v>0.00537530891597271</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.01881813816726208</v>
+        <v>0.007599097210913897</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.02002672664821148</v>
+        <v>0.001793899573385715</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.01568160392343998</v>
+        <v>0.0004194350622128695</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.01898764632642269</v>
+        <v>0.008137532509863377</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.001258724485523999</v>
+        <v>0.002038914943113923</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.02533986791968346</v>
+        <v>0.003413701895624399</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.01507561001926661</v>
+        <v>0.0003861793084070086</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.002614864148199558</v>
+        <v>0.003260476980358362</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.002185240387916565</v>
+        <v>0.004442424047738314</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.01555515080690384</v>
+        <v>0.0007399995811283588</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.008062803186476231</v>
+        <v>0.002363289939239621</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.008044357411563396</v>
+        <v>0.00711392518132925</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.03174920380115509</v>
+        <v>0.007293949835002422</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.00461122440174222</v>
+        <v>0.005739179439842701</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.004660150967538357</v>
+        <v>0.003781303530558944</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.01134719140827656</v>
+        <v>0.003847270272672176</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.001610247301869094</v>
+        <v>0.003745898371562362</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.008874348364770412</v>
+        <v>0.004779897630214691</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.03510676324367523</v>
+        <v>0.01356042921543121</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.01036130171269178</v>
+        <v>0.001752487383782864</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.009376429952681065</v>
+        <v>0.004865651950240135</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.002315784338861704</v>
+        <v>0.002021461725234985</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.008686968125402927</v>
+        <v>0.001927069271914661</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.003128109965473413</v>
+        <v>0.001212611445225775</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.009123066440224648</v>
+        <v>0.002182640368118882</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.002319398103281856</v>
+        <v>0.002530572935938835</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.00199244124814868</v>
+        <v>0.0023274184204638</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.01682566292583942</v>
+        <v>0.005055523943156004</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.0040229307487607</v>
+        <v>0.001411746721714735</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.005765066947788</v>
+        <v>0.002536115702241659</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.001337431604042649</v>
+        <v>0.002738678362220526</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.002622856292873621</v>
+        <v>0.003332872875034809</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.01010463200509548</v>
+        <v>0.0007802120526321232</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.003404552349820733</v>
+        <v>0.002470347797498107</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.00251235137693584</v>
+        <v>0.004115530289709568</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0231282040476799</v>
+        <v>0.002907382789999247</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.02109247259795666</v>
+        <v>0.01208397559821606</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.0003412773367017508</v>
+        <v>0.004288767464458942</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.002442231867462397</v>
+        <v>0.004859238397330046</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.01237160339951515</v>
+        <v>0.002203372772783041</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.00650890776887536</v>
+        <v>0.00404292531311512</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.0004581368993967772</v>
+        <v>0.004378512967377901</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.01031607016921043</v>
+        <v>0.002685060258954763</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.008263002149760723</v>
+        <v>0.003108959179371595</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.003392189508304</v>
+        <v>0.001944953808560967</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.01443636976182461</v>
+        <v>0.00557069992646575</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.007786969654262066</v>
+        <v>0.001174915465526283</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.01178064197301865</v>
+        <v>0.001587177161127329</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.001975951250642538</v>
+        <v>0.0026928442530334</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.00347428279928863</v>
+        <v>0.003355528460815549</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.01042632292956114</v>
+        <v>0.001688760588876903</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.0005888182204216719</v>
+        <v>0.00337705435231328</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.001919529400765896</v>
+        <v>0.004236851818859577</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.008094305172562599</v>
+        <v>0.0002202524337917566</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.05175519734621048</v>
+        <v>0.003221152815967798</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.01186196506023407</v>
+        <v>0.003697509178891778</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.02261410281062126</v>
+        <v>0.002240103669464588</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0008302805945277214</v>
+        <v>0.003058745292946696</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.002679737750440836</v>
+        <v>0.001418447704054415</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.004892034456133842</v>
+        <v>0.004473368637263775</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.005422018934041262</v>
+        <v>0.005164551548659801</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0127839557826519</v>
+        <v>0.0003548464737832546</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.003203061642125249</v>
+        <v>0.002779642585664988</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.01182689238339663</v>
+        <v>0.001697726896964014</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.009104594588279724</v>
+        <v>0.001559858210384846</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.00334674259647727</v>
+        <v>0.006646599154919386</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.006146963685750961</v>
+        <v>0.003645912278443575</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.01136604230850935</v>
+        <v>0.007938932627439499</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.005985320545732975</v>
+        <v>0.003923533484339714</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.006420610938221216</v>
+        <v>0.004273838829249144</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.01141782850027084</v>
+        <v>0.00770758418366313</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.004350312054157257</v>
+        <v>0.001863067387603223</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.01089336443692446</v>
+        <v>0.002026475965976715</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.0009525959030725062</v>
+        <v>0.002523063216358423</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.006476889830082655</v>
+        <v>0.002215063665062189</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.008725060150027275</v>
+        <v>0.003923976793885231</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.00287175877019763</v>
+        <v>0.01087189093232155</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.004885551519691944</v>
+        <v>0.001083432231098413</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.008141721598803997</v>
+        <v>0.001577967661432922</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.004393181297928095</v>
+        <v>0.0008067219750955701</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.005522574298083782</v>
+        <v>0.001416266313754022</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.002962387632578611</v>
+        <v>0.005973126739263535</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.003929090220481157</v>
+        <v>0.002168909180909395</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.01162585243582726</v>
+        <v>0.001806051703169942</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.005236475728452206</v>
+        <v>0.001611480838619173</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.001346367411315441</v>
+        <v>0.002937728073447943</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.004757558461278677</v>
+        <v>0.001824356615543365</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.005140397697687149</v>
+        <v>0.001348307239823043</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.0002097319375025108</v>
+        <v>0.00370672857388854</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.008196655660867691</v>
+        <v>0.003509177826344967</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.005122704897075891</v>
+        <v>0.002951043890789151</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.01410279888659716</v>
+        <v>3.224893589504063e-05</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.01231016684323549</v>
+        <v>0.008751355111598969</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.005144945811480284</v>
+        <v>0.0004504699318204075</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.0006180709460750222</v>
+        <v>0.0005535663804039359</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.00539251696318388</v>
+        <v>0.0007748439675197005</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.007251628674566746</v>
+        <v>0.001361732836812735</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.006826786790043116</v>
+        <v>0.0005731682758778334</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.003749007824808359</v>
+        <v>0.001467525260522962</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.01440275739878416</v>
+        <v>0.006116824224591255</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.006098374258726835</v>
+        <v>0.000803991686552763</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.008019950240850449</v>
+        <v>0.0008256842847913504</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.0005602209712378681</v>
+        <v>0.00190024555195123</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.0002330376737518236</v>
+        <v>0.00287395273335278</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.01220639050006866</v>
+        <v>0.0006062646280042827</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.003904885379597545</v>
+        <v>0.002823717659339309</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.001111836638301611</v>
+        <v>0.004127864725887775</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.005339218769222498</v>
+        <v>0.005311734043061733</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.007900181226432323</v>
+        <v>0.002679819706827402</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.003610711777582765</v>
+        <v>0.005400004331022501</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.009405734948813915</v>
+        <v>0.003030235879123211</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.007550651673227549</v>
+        <v>0.002061697654426098</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.004956724587827921</v>
+        <v>0.007489211857318878</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.002304251305758953</v>
+        <v>0.001153409830294549</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.001062204129993916</v>
+        <v>0.004542371723800898</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.003333446569740772</v>
+        <v>0.01388076413422823</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.01060066372156143</v>
+        <v>0.0046445457264781</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.00537531916052103</v>
+        <v>0.0107788210734725</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.01578101329505444</v>
+        <v>0.009176043793559074</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.008619155734777451</v>
+        <v>0.006344391033053398</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.02285048924386501</v>
+        <v>0.008522181771695614</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.008902127854526043</v>
+        <v>0.006828964687883854</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.01211500726640224</v>
+        <v>0.006198665592819452</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.003402161877602339</v>
+        <v>0.005628124345093966</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.007895706221461296</v>
+        <v>0.0006300553795881569</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.008718960918486118</v>
+        <v>0.002787510864436626</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.01088177971541882</v>
+        <v>0.004452687688171864</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.004978322423994541</v>
+        <v>0.005015263799577951</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.01742524467408657</v>
+        <v>0.003121478715911508</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.01102159358561039</v>
+        <v>0.01222678553313017</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.01941301487386227</v>
+        <v>0.001501286053098738</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.01254840102046728</v>
+        <v>0.003488450543954968</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.01155707146972418</v>
+        <v>0.003496929071843624</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.002818248700350523</v>
+        <v>0.0009993305429816246</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.009510093368589878</v>
+        <v>0.05005821958184242</v>
       </c>
       <c r="B13" t="n">
-        <v>0.09655767679214478</v>
+        <v>0.194803923368454</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01717576943337917</v>
+        <v>0.04792609810829163</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02250517345964909</v>
+        <v>0.02240650355815887</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0462164431810379</v>
+        <v>0.06168974936008453</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00417516240850091</v>
+        <v>0.1333550363779068</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01696365512907505</v>
+        <v>0.03695067763328552</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02013400197029114</v>
+        <v>0.06496892124414444</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0354795977473259</v>
+        <v>0.02590961754322052</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01606898754835129</v>
+        <v>0.00942483264952898</v>
       </c>
       <c r="K13" t="n">
-        <v>0.07410845905542374</v>
+        <v>0.249394565820694</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01148559805005789</v>
+        <v>0.04906520247459412</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02961399033665657</v>
+        <v>0.02476103603839874</v>
       </c>
       <c r="N13" t="n">
-        <v>0.05362372100353241</v>
+        <v>0.09961175918579102</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01571210287511349</v>
+        <v>0.1367059201002121</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0008354815654456615</v>
+        <v>0.03885533660650253</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.009941733442246914</v>
+        <v>0.003391345962882042</v>
       </c>
       <c r="R13" t="n">
-        <v>0.03212040662765503</v>
+        <v>0.02373337186872959</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001868426916189492</v>
+        <v>0.01192572340369225</v>
       </c>
       <c r="T13" t="n">
-        <v>0.02062928304076195</v>
+        <v>0.03122616373002529</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01001144852489233</v>
+        <v>0.002124077640473843</v>
       </c>
       <c r="V13" t="n">
-        <v>0.008936729282140732</v>
+        <v>0.07101549953222275</v>
       </c>
       <c r="W13" t="n">
-        <v>0.005682571791112423</v>
+        <v>0.04514453187584877</v>
       </c>
       <c r="X13" t="n">
-        <v>0.00639746617525816</v>
+        <v>0.03002936951816082</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.007158709224313498</v>
+        <v>0.002943618688732386</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.006486047990620136</v>
+        <v>0.001535209827125072</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.007686734199523926</v>
+        <v>0.04305282607674599</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.01183822005987167</v>
+        <v>0.01596991345286369</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.02254992350935936</v>
+        <v>0.02177445776760578</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.007618991658091545</v>
+        <v>0.04080638289451599</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.002527008298784494</v>
+        <v>0.04536844044923782</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01263065170496702</v>
+        <v>0.04697614163160324</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.01192865334451199</v>
+        <v>0.05185947939753532</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.002930035581812263</v>
+        <v>0.01215779781341553</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.006364138796925545</v>
+        <v>0.08592745661735535</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.001434583216905594</v>
+        <v>0.0112359207123518</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.01117778848856688</v>
+        <v>0.007753271143883467</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01299231220036745</v>
+        <v>0.07528130710124969</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.007020768243819475</v>
+        <v>0.02474126406013966</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.003831790527328849</v>
+        <v>0.0328136682510376</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.005564486607909203</v>
+        <v>0.04963343963027</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.01295973919332027</v>
+        <v>0.02314918488264084</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.003233186900615692</v>
+        <v>0.005873417481780052</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.001427572220563889</v>
+        <v>0.02191535569727421</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.001120046945288777</v>
+        <v>0.008790786378085613</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0009205953683704138</v>
+        <v>0.01040923595428467</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.06518198549747467</v>
+        <v>0.2597405016422272</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.007050624582916498</v>
+        <v>0.01212056167423725</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.00134444423019886</v>
+        <v>0.01302528195083141</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.007755333557724953</v>
+        <v>0.02704298496246338</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.006528975442051888</v>
+        <v>0.07815586030483246</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.01225195359438658</v>
+        <v>0.01835495978593826</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.008420933969318867</v>
+        <v>0.0131140761077404</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.006608277559280396</v>
+        <v>0.006721071433275938</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.00664726784452796</v>
+        <v>0.06209466233849525</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0220164954662323</v>
+        <v>0.05887499824166298</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.01418343558907509</v>
+        <v>0.05869709700345993</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.007118946872651577</v>
+        <v>0.04159673675894737</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.03241662681102753</v>
+        <v>0.05505708605051041</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.01114979386329651</v>
+        <v>0.001763296429999173</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.003713973565027118</v>
+        <v>0.01466112583875656</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.007189561147242785</v>
+        <v>0.04004522413015366</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.02095616422593594</v>
+        <v>0.009755190461874008</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0128604443743825</v>
+        <v>0.01113247312605381</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.006636200938373804</v>
+        <v>0.03048711642622948</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.002012678189203143</v>
+        <v>0.005327204708009958</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.0134738115593791</v>
+        <v>0.03795652091503143</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.02549492940306664</v>
+        <v>0.02993623539805412</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01574151217937469</v>
+        <v>0.02708452939987183</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.003743730019778013</v>
+        <v>0.09589224308729172</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.00352715770713985</v>
+        <v>0.009718392975628376</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.001726449932903051</v>
+        <v>0.008101482875645161</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.002180743729695678</v>
+        <v>0.01608294993638992</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.04138952121138573</v>
+        <v>0.1599957048892975</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.01401799358427525</v>
+        <v>0.01623566634953022</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.008315503597259521</v>
+        <v>0.07746297121047974</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.001698511186987162</v>
+        <v>0.04117228835821152</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.006143763661384583</v>
+        <v>0.05276848748326302</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.003800788428634405</v>
+        <v>0.01348436810076237</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.002766541671007872</v>
+        <v>0.003532503498718143</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.01073886826634407</v>
+        <v>0.04055990278720856</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0007561325328424573</v>
+        <v>0.004316487815231085</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.01823454722762108</v>
+        <v>0.07644059509038925</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0004544503754004836</v>
+        <v>0.0183444619178772</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.003442846704274416</v>
+        <v>0.01168213039636612</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.002888413844630122</v>
+        <v>0.005658678710460663</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.00247122161090374</v>
+        <v>0.02839445322751999</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.002489823149517179</v>
+        <v>0.02102841250598431</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.00122647697571665</v>
+        <v>0.003899143077433109</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.009639543481171131</v>
+        <v>0.001456928788684309</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.02325794659554958</v>
+        <v>0.04956891015172005</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.02310632169246674</v>
+        <v>0.126742348074913</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.002179915318265557</v>
+        <v>0.07008309662342072</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.0005522834253497422</v>
+        <v>0.06844449043273926</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0110450005158782</v>
+        <v>0.03126855939626694</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.002687999978661537</v>
+        <v>0.01435191184282303</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.01318810414522886</v>
+        <v>0.043232262134552</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.01930676773190498</v>
+        <v>0.01993524096906185</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.009122146293520927</v>
+        <v>0.001916902838274837</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.001063569448888302</v>
+        <v>0.01843994297087193</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.01568129472434521</v>
+        <v>0.06829656660556793</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.002831948222592473</v>
+        <v>0.01868487894535065</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.003915234934538603</v>
+        <v>0.00161689193919301</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.004744836129248142</v>
+        <v>0.00526692159473896</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0002817504573613405</v>
+        <v>0.02700627781450748</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.002066545886918902</v>
+        <v>0.01157357450574636</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0003126662923023105</v>
+        <v>0.0004962114617228508</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.006076045334339142</v>
+        <v>0.007243298925459385</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.001960840309038758</v>
+        <v>0.05534190684556961</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.02873320877552032</v>
+        <v>0.05631661415100098</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.0100919883698225</v>
+        <v>0.005009101703763008</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.02442017756402493</v>
+        <v>0.05511243268847466</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0134805953130126</v>
+        <v>0.009510554373264313</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.006094323471188545</v>
+        <v>0.06087923049926758</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.01394497975707054</v>
+        <v>0.01638021506369114</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.01418856251984835</v>
+        <v>0.07551717758178711</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.005164207424968481</v>
+        <v>0.01322635263204575</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.002049230737611651</v>
+        <v>0.004292613826692104</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.003708860836923122</v>
+        <v>0.02607906237244606</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.005311193410307169</v>
+        <v>0.01605524867773056</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.003548454958945513</v>
+        <v>0.04072931408882141</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.003110840916633606</v>
+        <v>0.02168120071291924</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0009126164368353784</v>
+        <v>0.02545446716248989</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.009609474800527096</v>
+        <v>0.002809932455420494</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.004506038967519999</v>
+        <v>0.03558771312236786</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.001970056211575866</v>
+        <v>0.01407177187502384</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.002343467669561505</v>
+        <v>0.02681507170200348</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.01238168776035309</v>
+        <v>0.04750915616750717</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.002247067634016275</v>
+        <v>0.0406588613986969</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.001799936173483729</v>
+        <v>0.01483284682035446</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.009779819287359715</v>
+        <v>0.03732576966285706</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0006615293677896261</v>
+        <v>0.06919757276773453</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.002641757950186729</v>
+        <v>0.01584157906472683</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.009662722237408161</v>
+        <v>0.03976853564381599</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.005516600795090199</v>
+        <v>0.03541166335344315</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.001645521144382656</v>
+        <v>0.02839205600321293</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.008598245680332184</v>
+        <v>0.02329566143453121</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.0008361140498891473</v>
+        <v>0.01208165567368269</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.0006024891627021134</v>
+        <v>0.02074266783893108</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.009512763470411301</v>
+        <v>0.01664720103144646</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.001043186290189624</v>
+        <v>0.02509256638586521</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.005789429880678654</v>
+        <v>0.001960457768291235</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0006387076573446393</v>
+        <v>0.003744443645700812</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.01249674148857594</v>
+        <v>0.006093110423535109</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.007445856928825378</v>
+        <v>0.003970569930970669</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.01538323145359755</v>
+        <v>0.05306409299373627</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.008267519995570183</v>
+        <v>0.03868523612618446</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.003683274611830711</v>
+        <v>0.004636842757463455</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.001615690300241113</v>
+        <v>0.02259852923452854</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.002012830693274736</v>
+        <v>0.002998202107846737</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.005337468348443508</v>
+        <v>0.01817918568849564</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0007582467515021563</v>
+        <v>0.02125020325183868</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.0001550945453345776</v>
+        <v>0.03628358617424965</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.001662405207753181</v>
+        <v>0.007810152601450682</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0191306471824646</v>
+        <v>0.08415599912405014</v>
       </c>
       <c r="EZ13" t="n">
-        <v>9.769821917871013e-05</v>
+        <v>0.02013222500681877</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.003537630662322044</v>
+        <v>0.001675436273217201</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.004534599371254444</v>
+        <v>0.002504063304513693</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.002856881823390722</v>
+        <v>0.03125037252902985</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0005764765664935112</v>
+        <v>0.02517641149461269</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.001465526176616549</v>
+        <v>0.004610682837665081</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.005513884592801332</v>
+        <v>0.01403809804469347</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0009943998884409666</v>
+        <v>0.02219177037477493</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.007808650378137827</v>
+        <v>0.04483738169074059</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.004814980085939169</v>
+        <v>0.003042074618861079</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.004461749922484159</v>
+        <v>0.03957782313227654</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.002572402358055115</v>
+        <v>0.02094811946153641</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.001020413124933839</v>
+        <v>0.01910494826734066</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.005561105441302061</v>
+        <v>0.01538729015737772</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.001063031377270818</v>
+        <v>0.05711105465888977</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.00812858808785677</v>
+        <v>0.01865942403674126</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.005472386255860329</v>
+        <v>0.03833258152008057</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.00673148687928915</v>
+        <v>0.06537425518035889</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.009074188768863678</v>
+        <v>0.0157613679766655</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.01319612469524145</v>
+        <v>0.03831794857978821</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.006163143087178469</v>
+        <v>0.04739940166473389</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.01286548841744661</v>
+        <v>0.01758299022912979</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.01378449331969023</v>
+        <v>0.009008251130580902</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.009960221126675606</v>
+        <v>0.06309020519256592</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.006187033839523792</v>
+        <v>0.009750274941325188</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.01182000525295734</v>
+        <v>0.006980760954320431</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.01267229672521353</v>
+        <v>0.01668992266058922</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.006159040611237288</v>
+        <v>0.02408109232783318</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.006281347014009953</v>
+        <v>0.01940238103270531</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.01112161856144667</v>
+        <v>0.03108126297593117</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.01436903513967991</v>
+        <v>0.04759829863905907</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.01072284579277039</v>
+        <v>0.01513731759041548</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.005636589601635933</v>
+        <v>0.02507731691002846</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.003100052941590548</v>
+        <v>0.02635150030255318</v>
       </c>
     </row>
     <row r="14">
@@ -8396,2278 +8396,2278 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.05218959227204323</v>
+        <v>0.1870186626911163</v>
       </c>
       <c r="B15" t="n">
-        <v>0.6639389991760254</v>
+        <v>0.1837215423583984</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5591022968292236</v>
+        <v>0.3947401642799377</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2630481719970703</v>
+        <v>0.4562845230102539</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7724147439002991</v>
+        <v>0.3444733917713165</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08604203164577484</v>
+        <v>0.08561608195304871</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2994252741336823</v>
+        <v>0.1168685406446457</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2428047955036163</v>
+        <v>0.009210921823978424</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3379888832569122</v>
+        <v>0.08141165226697922</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1392220854759216</v>
+        <v>0.1760798096656799</v>
       </c>
       <c r="K15" t="n">
-        <v>0.468994677066803</v>
+        <v>0.3228300213813782</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3678843379020691</v>
+        <v>0.2965346276760101</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2026888430118561</v>
+        <v>0.3289541006088257</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8540152907371521</v>
+        <v>0.3063007295131683</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1411975175142288</v>
+        <v>0.116089902818203</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2840638160705566</v>
+        <v>0.09826650470495224</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1649882793426514</v>
+        <v>0.004217520356178284</v>
       </c>
       <c r="R15" t="n">
-        <v>0.263327956199646</v>
+        <v>0.1390902996063232</v>
       </c>
       <c r="S15" t="n">
-        <v>0.03119376488029957</v>
+        <v>0.09391158074140549</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1216165199875832</v>
+        <v>0.1820081770420074</v>
       </c>
       <c r="U15" t="n">
-        <v>0.006534671410918236</v>
+        <v>0.2233102321624756</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1744429767131805</v>
+        <v>0.1040661931037903</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1051153093576431</v>
+        <v>0.07354893535375595</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1552974879741669</v>
+        <v>0.08758828043937683</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.007887645624577999</v>
+        <v>0.02538721822202206</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.1265004873275757</v>
+        <v>0.1092879101634026</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0658579021692276</v>
+        <v>0.1015039160847664</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.07471615076065063</v>
+        <v>0.1176464408636093</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1712130606174469</v>
+        <v>0.02879663556814194</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.004251431673765182</v>
+        <v>0.2024655342102051</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.1110864207148552</v>
+        <v>0.07773915678262711</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0648442804813385</v>
+        <v>0.02111659944057465</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.1374839544296265</v>
+        <v>0.1068660467863083</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.0172446072101593</v>
+        <v>0.0189029835164547</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.06923212856054306</v>
+        <v>0.1703078895807266</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.02671600319445133</v>
+        <v>0.1146258339285851</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.01060542277991772</v>
+        <v>0.09574317187070847</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.3619006872177124</v>
+        <v>0.3676385283470154</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.008203327655792236</v>
+        <v>0.001006940379738808</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.07283881306648254</v>
+        <v>0.0416603609919548</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.01783988624811172</v>
+        <v>0.3798158168792725</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.1507122963666916</v>
+        <v>0.0456862598657608</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.02686667814850807</v>
+        <v>0.04143675416707993</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.04643086344003677</v>
+        <v>0.009227689355611801</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.1124114692211151</v>
+        <v>0.01025373116135597</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.1904490441083908</v>
+        <v>0.1219951137900352</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.6124455332756042</v>
+        <v>0.4542442858219147</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.3739569783210754</v>
+        <v>0.1572204828262329</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.05484581738710403</v>
+        <v>0.2320185005664825</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.144161194562912</v>
+        <v>0.3836586177349091</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.181226372718811</v>
+        <v>0.03430917114019394</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.003029882907867432</v>
+        <v>0.0006301579996943474</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.01434147264808416</v>
+        <v>0.2020727246999741</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.12713323533535</v>
+        <v>0.1348747462034225</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.03812593594193459</v>
+        <v>0.09053085744380951</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.02246520295739174</v>
+        <v>0.6593280434608459</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.05975838005542755</v>
+        <v>0.3970875442028046</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.294916570186615</v>
+        <v>0.1135324612259865</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.6350424885749817</v>
+        <v>0.9905070066452026</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.02576234564185143</v>
+        <v>0.1071792542934418</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.1638778746128082</v>
+        <v>0.08475854992866516</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.08189292252063751</v>
+        <v>0.1675047874450684</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.1762715876102448</v>
+        <v>0.07787933200597763</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.2276044338941574</v>
+        <v>0.1181508600711823</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.2256065011024475</v>
+        <v>0.06324930489063263</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.05202276259660721</v>
+        <v>0.1099272817373276</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.06353402137756348</v>
+        <v>0.000731966458261013</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.142497256398201</v>
+        <v>0.07318674772977829</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.1685353815555573</v>
+        <v>0.1145743131637573</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.1535047292709351</v>
+        <v>0.02909053862094879</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.09425537288188934</v>
+        <v>0.008828956633806229</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.1136693358421326</v>
+        <v>0.08430451154708862</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.1422877311706543</v>
+        <v>0.1874464005231857</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.3357929587364197</v>
+        <v>0.4619515240192413</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.4011074602603912</v>
+        <v>0.1595036834478378</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.001990869641304016</v>
+        <v>0.02301547303795815</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.1276033818721771</v>
+        <v>0.04793672263622284</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.1033441498875618</v>
+        <v>0.1736891120672226</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.0507892519235611</v>
+        <v>0.07213781028985977</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.02929332666099072</v>
+        <v>0.0307556539773941</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.01007702108472586</v>
+        <v>0.03948625177145004</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.003939684480428696</v>
+        <v>0.1100696921348572</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.09711147844791412</v>
+        <v>0.1891108751296997</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.07462888211011887</v>
+        <v>0.07080122828483582</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.1356567442417145</v>
+        <v>0.09093886613845825</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.1650910377502441</v>
+        <v>0.0732862651348114</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.04016997292637825</v>
+        <v>0.0041695237159729</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.002734667155891657</v>
+        <v>0.03462115302681923</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.07057437300682068</v>
+        <v>0.01242643967270851</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.07475736737251282</v>
+        <v>0.009766751900315285</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.1604124754667282</v>
+        <v>0.1221259981393814</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.1075641512870789</v>
+        <v>0.02365496754646301</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.03148508071899414</v>
+        <v>0.03665437176823616</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.2505121827125549</v>
+        <v>0.2126848995685577</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.2029819339513779</v>
+        <v>0.5123031735420227</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.1084140539169312</v>
+        <v>0.1801932752132416</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.1530043184757233</v>
+        <v>0.1131796762347221</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.07349501550197601</v>
+        <v>0.09534934163093567</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.05772083625197411</v>
+        <v>0.01344612240791321</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.02789242379367352</v>
+        <v>0.08296898007392883</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.02960120141506195</v>
+        <v>0.1449970155954361</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.06428736448287964</v>
+        <v>0.08271130919456482</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.1093334332108498</v>
+        <v>0.05061749368906021</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.1397037506103516</v>
+        <v>0.06745747476816177</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.05896740779280663</v>
+        <v>0.04602183774113655</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.004545843228697777</v>
+        <v>0.04197010770440102</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.03705616295337677</v>
+        <v>0.05244700610637665</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.1297419816255569</v>
+        <v>0.07230454683303833</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.1451236605644226</v>
+        <v>0.1056027412414551</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.06052592024207115</v>
+        <v>0.2232690006494522</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.111933134496212</v>
+        <v>0.1414921134710312</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.3287102282047272</v>
+        <v>0.0499507300555706</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.02623368799686432</v>
+        <v>0.02908141165971756</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.0801827684044838</v>
+        <v>0.3393242657184601</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.09270770847797394</v>
+        <v>0.04283824563026428</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.1731627285480499</v>
+        <v>0.1339711248874664</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.1755460798740387</v>
+        <v>0.3361721634864807</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.09207641333341599</v>
+        <v>0.1306649893522263</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.0405266173183918</v>
+        <v>0.0656764805316925</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.04432159289717674</v>
+        <v>0.01518411561846733</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.1177288219332695</v>
+        <v>0.06080025434494019</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.1705664843320847</v>
+        <v>0.07583463191986084</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.193335235118866</v>
+        <v>0.1250995397567749</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.0179186575114727</v>
+        <v>0.01140930131077766</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.03929482027888298</v>
+        <v>0.04382529109716415</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.04848606139421463</v>
+        <v>0.05019977688789368</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.07708780467510223</v>
+        <v>0.03859640657901764</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.103641614317894</v>
+        <v>0.2521469593048096</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.0986253097653389</v>
+        <v>0.04632255434989929</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.07588973641395569</v>
+        <v>0.1915061622858047</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.1233604997396469</v>
+        <v>0.3728747665882111</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.2159357964992523</v>
+        <v>0.1012047007679939</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.01244691573083401</v>
+        <v>0.05358333885669708</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.07883644104003906</v>
+        <v>0.08679765462875366</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.01958679594099522</v>
+        <v>0.09174280613660812</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.04188919067382812</v>
+        <v>0.08221441507339478</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.05294055864214897</v>
+        <v>0.02119745314121246</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.04006074741482735</v>
+        <v>0.02208049222826958</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.05503078550100327</v>
+        <v>0.003694066777825356</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.1935387849807739</v>
+        <v>0.01144676841795444</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.05090682208538055</v>
+        <v>0.003300605341792107</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.1014216691255569</v>
+        <v>0.04373128339648247</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.02782638370990753</v>
+        <v>0.04836690053343773</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.1358129382133484</v>
+        <v>0.1184032410383224</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.05558568611741066</v>
+        <v>0.009090515784919262</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.04320904240012169</v>
+        <v>0.2012468576431274</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.09524765610694885</v>
+        <v>0.1907436698675156</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.105467215180397</v>
+        <v>0.01738796196877956</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.03955967351794243</v>
+        <v>0.0245157778263092</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.2116858065128326</v>
+        <v>0.03467508777976036</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.08251943439245224</v>
+        <v>0.0004024803638458252</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.119676411151886</v>
+        <v>0.07465148717164993</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.2533406913280487</v>
+        <v>0.0728527158498764</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.004690364003181458</v>
+        <v>0.1329893916845322</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.01514221075922251</v>
+        <v>0.1561238765716553</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.06034298986196518</v>
+        <v>0.05783110857009888</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.1474202871322632</v>
+        <v>0.087514728307724</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.1504799127578735</v>
+        <v>0.09390012174844742</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.08493278920650482</v>
+        <v>0.06032183393836021</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.02846724539995193</v>
+        <v>0.02377499639987946</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.1002113372087479</v>
+        <v>0.04792830348014832</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.05799296498298645</v>
+        <v>0.04724448919296265</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.05535709857940674</v>
+        <v>0.04780720919370651</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.2247912138700485</v>
+        <v>0.1629336923360825</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.165241926908493</v>
+        <v>0.264084130525589</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.07061266899108887</v>
+        <v>0.05681225657463074</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.1481965631246567</v>
+        <v>0.3111526966094971</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.00747954286634922</v>
+        <v>0.27840456366539</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.1609761416912079</v>
+        <v>0.003233783412724733</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.002479590009897947</v>
+        <v>0.07439032196998596</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.1205940693616867</v>
+        <v>0.191963329911232</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.00646006315946579</v>
+        <v>0.2076894640922546</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.1110849976539612</v>
+        <v>0.1702583134174347</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.2006742507219315</v>
+        <v>0.2433650344610214</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.3013356029987335</v>
+        <v>0.1855255216360092</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.02514823339879513</v>
+        <v>0.1372532844543457</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.0138313164934516</v>
+        <v>0.4262581169605255</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.1376892030239105</v>
+        <v>0.05200196802616119</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.2430970221757889</v>
+        <v>0.01755685359239578</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.02162348479032516</v>
+        <v>0.005175340920686722</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.1119570434093475</v>
+        <v>0.009240839630365372</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.05768051743507385</v>
+        <v>0.1319094747304916</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.1384185701608658</v>
+        <v>0.117778867483139</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.05690078064799309</v>
+        <v>0.1498584002256393</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.09088383615016937</v>
+        <v>0.01322054117918015</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.248469278216362</v>
+        <v>0.2655432820320129</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.1671352833509445</v>
+        <v>0.007365149445831776</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.392890065908432</v>
+        <v>0.1128411889076233</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.08752663433551788</v>
+        <v>0.03775617107748985</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.0001222966238856316</v>
+        <v>0.0002490761689841747</v>
       </c>
       <c r="B16" t="n">
-        <v>0.001227765460498631</v>
+        <v>0.01774256303906441</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0001147280418081209</v>
+        <v>0.001664388924837112</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0004184154677204788</v>
+        <v>0.006082348525524139</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0003169334377162158</v>
+        <v>0.001418498111888766</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0006492710672318935</v>
+        <v>0.008425658568739891</v>
       </c>
       <c r="G16" t="n">
-        <v>9.338773088529706e-05</v>
+        <v>0.008680370636284351</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0004099379293620586</v>
+        <v>0.006749499589204788</v>
       </c>
       <c r="I16" t="n">
-        <v>1.057146528182784e-05</v>
+        <v>0.001525963307358325</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0002130431239493191</v>
+        <v>0.003523448016494513</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00116207601968199</v>
+        <v>0.01609152369201183</v>
       </c>
       <c r="L16" t="n">
-        <v>1.752644948282978e-06</v>
+        <v>0.006837445311248302</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0002121409052051604</v>
+        <v>0.01578177325427532</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77903966687154e-05</v>
+        <v>0.008076192811131477</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0007082177326083183</v>
+        <v>0.01321405079215765</v>
       </c>
       <c r="P16" t="n">
-        <v>9.918778960127383e-05</v>
+        <v>0.007349336985498667</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0001337732537649572</v>
+        <v>0.001843139063566923</v>
       </c>
       <c r="R16" t="n">
-        <v>2.431667962810025e-05</v>
+        <v>0.008031720295548439</v>
       </c>
       <c r="S16" t="n">
-        <v>3.704642222146504e-05</v>
+        <v>0.001366771990433335</v>
       </c>
       <c r="T16" t="n">
-        <v>9.453498205402866e-05</v>
+        <v>0.007826181128621101</v>
       </c>
       <c r="U16" t="n">
-        <v>5.735898957937025e-05</v>
+        <v>0.0004871787969022989</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0001965978590305895</v>
+        <v>0.001101715373806655</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0001374567509628832</v>
+        <v>0.001969621516764164</v>
       </c>
       <c r="X16" t="n">
-        <v>1.280580136153731e-06</v>
+        <v>0.002026720205321908</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.830196535796858e-05</v>
+        <v>0.00229256646707654</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0001142663531936705</v>
+        <v>0.003994583617895842</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.771936487988569e-05</v>
+        <v>0.001724101253785193</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.954306208062917e-05</v>
+        <v>0.001369598903693259</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.534090168017428e-06</v>
+        <v>0.0009191252756863832</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.202523268759251e-05</v>
+        <v>0.001748165814206004</v>
       </c>
       <c r="AE16" t="n">
-        <v>9.826861787587404e-05</v>
+        <v>0.00435996800661087</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0001063531526597217</v>
+        <v>0.004176993388682604</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.452786793583073e-05</v>
+        <v>0.01202117092907429</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.182601383537985e-05</v>
+        <v>0.002448933199048042</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0001236840325873345</v>
+        <v>0.01452166587114334</v>
       </c>
       <c r="AJ16" t="n">
-        <v>8.727735257707536e-05</v>
+        <v>0.0007111362647265196</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.0002234852145193145</v>
+        <v>0.0005705496296286583</v>
       </c>
       <c r="AL16" t="n">
-        <v>7.549415022367612e-05</v>
+        <v>0.004196641966700554</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.709114985715132e-05</v>
+        <v>0.0008276910521090031</v>
       </c>
       <c r="AN16" t="n">
-        <v>4.986188287148252e-06</v>
+        <v>0.001028810627758503</v>
       </c>
       <c r="AO16" t="n">
-        <v>6.526744255097583e-05</v>
+        <v>0.0006637610495090485</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.0001762282336130738</v>
+        <v>0.0009413590305484831</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.773501470685005e-05</v>
+        <v>0.0004171476466581225</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.0001148187293438241</v>
+        <v>0.009617027826607227</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.0001388714590575546</v>
+        <v>0.003523246850818396</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.787212179100607e-05</v>
+        <v>0.002130705863237381</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.0006721630343236029</v>
+        <v>0.0164620503783226</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.0001750680967234075</v>
+        <v>0.003001864068210125</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.29321439191699e-05</v>
+        <v>0.004144966602325439</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.0002133668604074046</v>
+        <v>0.009466773830354214</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.0002688207314349711</v>
+        <v>0.01463058684021235</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9.215405589202419e-05</v>
+        <v>0.0002292903373017907</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.000190386243048124</v>
+        <v>0.005554107017815113</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.24327687243931e-05</v>
+        <v>0.0006658259080722928</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.65956109110266e-05</v>
+        <v>0.001719454186968505</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.0002765774261206388</v>
+        <v>0.0009234714088961482</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.000341088802088052</v>
+        <v>0.004312734119594097</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.619170663820114e-05</v>
+        <v>0.003478062571957707</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.042492845561355e-05</v>
+        <v>0.003331747371703386</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.0001457573962397873</v>
+        <v>0.005710136145353317</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.0001243138976860791</v>
+        <v>0.002985223662108183</v>
       </c>
       <c r="BJ16" t="n">
-        <v>5.124988092575222e-05</v>
+        <v>0.002520095556974411</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.615827128873207e-05</v>
+        <v>0.0002333911834284663</v>
       </c>
       <c r="BL16" t="n">
-        <v>8.16329920780845e-05</v>
+        <v>6.29468122497201e-05</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.000166645462741144</v>
+        <v>0.004280311055481434</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.0001415189472027123</v>
+        <v>0.003537935204803944</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.15092911478132e-05</v>
+        <v>0.004071926698088646</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.605415597325191e-05</v>
+        <v>0.001013997360132635</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.695286068250425e-05</v>
+        <v>0.0005828518769703805</v>
       </c>
       <c r="BR16" t="n">
-        <v>8.508913015248254e-05</v>
+        <v>0.00307749561034143</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.468098531011492e-05</v>
+        <v>0.002216070657595992</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.0001743971515679732</v>
+        <v>0.004134047776460648</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.198112972313538e-05</v>
+        <v>0.0001128595322370529</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.0004051954892929643</v>
+        <v>0.01418823562562466</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.0001322142197750509</v>
+        <v>0.002141454722732306</v>
       </c>
       <c r="BX16" t="n">
-        <v>2.108455373672768e-05</v>
+        <v>0.003032900858670473</v>
       </c>
       <c r="BY16" t="n">
-        <v>9.087991202250123e-05</v>
+        <v>0.0008217720314860344</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.0001706884359009564</v>
+        <v>0.002516851527616382</v>
       </c>
       <c r="CA16" t="n">
-        <v>2.61152526945807e-05</v>
+        <v>0.004766740836203098</v>
       </c>
       <c r="CB16" t="n">
-        <v>7.776442362228408e-05</v>
+        <v>0.001682918751612306</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.702947131183464e-05</v>
+        <v>0.001536247204057872</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.063707092427649e-05</v>
+        <v>0.0005746616516262293</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.0002316952595720068</v>
+        <v>0.00694715790450573</v>
       </c>
       <c r="CF16" t="n">
-        <v>9.10426679183729e-05</v>
+        <v>0.001744050881825387</v>
       </c>
       <c r="CG16" t="n">
-        <v>7.471168646588922e-05</v>
+        <v>0.002471690531820059</v>
       </c>
       <c r="CH16" t="n">
-        <v>4.502115916693583e-05</v>
+        <v>0.0006353378994390368</v>
       </c>
       <c r="CI16" t="n">
-        <v>5.32908015884459e-05</v>
+        <v>0.001401972840540111</v>
       </c>
       <c r="CJ16" t="n">
-        <v>7.364317571045831e-05</v>
+        <v>0.0004135666531510651</v>
       </c>
       <c r="CK16" t="n">
-        <v>9.486400813329965e-05</v>
+        <v>0.001078129047527909</v>
       </c>
       <c r="CL16" t="n">
-        <v>6.3011706515681e-05</v>
+        <v>0.001167786307632923</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.0002660157042555511</v>
+        <v>0.002196633955463767</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.0001149611562141217</v>
+        <v>0.008425061590969563</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.363318460789742e-05</v>
+        <v>0.005527655594050884</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.0001936618064064533</v>
+        <v>0.009344637393951416</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.0001411924313288182</v>
+        <v>0.004516700282692909</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.0003041661693714559</v>
+        <v>0.00409997021779418</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.0002187256322940812</v>
+        <v>0.002630846574902534</v>
       </c>
       <c r="CT16" t="n">
-        <v>6.291978934314102e-05</v>
+        <v>0.001378951827064157</v>
       </c>
       <c r="CU16" t="n">
-        <v>6.995085277594626e-05</v>
+        <v>0.003568800864741206</v>
       </c>
       <c r="CV16" t="n">
-        <v>3.562297206372023e-05</v>
+        <v>0.0005206188652664423</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.0002248168748337775</v>
+        <v>0.006241001188755035</v>
       </c>
       <c r="CX16" t="n">
-        <v>0.0001179985047201626</v>
+        <v>0.00226484052836895</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.0001264748279936612</v>
+        <v>0.004250071942806244</v>
       </c>
       <c r="CZ16" t="n">
-        <v>4.457554678083397e-05</v>
+        <v>0.0006114655407145619</v>
       </c>
       <c r="DA16" t="n">
-        <v>7.356493006227538e-05</v>
+        <v>0.002641635714098811</v>
       </c>
       <c r="DB16" t="n">
-        <v>6.828393816249445e-05</v>
+        <v>0.0004051337018609047</v>
       </c>
       <c r="DC16" t="n">
-        <v>0.000153816508827731</v>
+        <v>0.001147745177149773</v>
       </c>
       <c r="DD16" t="n">
-        <v>4.992583853891119e-05</v>
+        <v>0.0003503121843095869</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.000134728557895869</v>
+        <v>0.001318100490607321</v>
       </c>
       <c r="DF16" t="n">
-        <v>6.056554411770776e-05</v>
+        <v>0.0123511515557766</v>
       </c>
       <c r="DG16" t="n">
-        <v>5.985329607938183e-06</v>
+        <v>0.0105122122913599</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.0004463793593458831</v>
+        <v>0.002209892263635993</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.0004784912161994725</v>
+        <v>0.001377850654534996</v>
       </c>
       <c r="DJ16" t="n">
-        <v>9.554116695653647e-05</v>
+        <v>0.01451426651328802</v>
       </c>
       <c r="DK16" t="n">
-        <v>0.000145919038914144</v>
+        <v>0.002224270720034838</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.0001485100801801309</v>
+        <v>0.009662425145506859</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.0001732880191411823</v>
+        <v>0.001143118017353117</v>
       </c>
       <c r="DN16" t="n">
-        <v>6.103271516622044e-05</v>
+        <v>0.001306210528127849</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.0001336261921096593</v>
+        <v>0.005080540664494038</v>
       </c>
       <c r="DP16" t="n">
-        <v>8.341289503732696e-05</v>
+        <v>0.002337607555091381</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.0001267509796889499</v>
+        <v>0.0001436119200661778</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.858214328531176e-05</v>
+        <v>0.002093600342050195</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.0001089543802663684</v>
+        <v>0.001897551119327545</v>
       </c>
       <c r="DT16" t="n">
-        <v>7.689940684940666e-05</v>
+        <v>7.369881495833397e-05</v>
       </c>
       <c r="DU16" t="n">
-        <v>0.0001393080892739818</v>
+        <v>0.006679916754364967</v>
       </c>
       <c r="DV16" t="n">
-        <v>5.100380803924054e-05</v>
+        <v>0.001390866120345891</v>
       </c>
       <c r="DW16" t="n">
-        <v>2.888176823034883e-06</v>
+        <v>0.001024839584715664</v>
       </c>
       <c r="DX16" t="n">
-        <v>6.496917194453999e-05</v>
+        <v>0.002321386011317372</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.0001153700577560812</v>
+        <v>0.002564246067777276</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.120293306186795e-05</v>
+        <v>0.001546032726764679</v>
       </c>
       <c r="EA16" t="n">
-        <v>7.127761637093499e-05</v>
+        <v>0.004234123509377241</v>
       </c>
       <c r="EB16" t="n">
-        <v>3.273194670327939e-05</v>
+        <v>0.002204249845817685</v>
       </c>
       <c r="EC16" t="n">
-        <v>8.220136805903167e-05</v>
+        <v>0.001282639685086906</v>
       </c>
       <c r="ED16" t="n">
-        <v>2.464192220941186e-06</v>
+        <v>0.00916888564825058</v>
       </c>
       <c r="EE16" t="n">
-        <v>9.224185487255454e-05</v>
+        <v>0.01158724073320627</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.0001804572239052504</v>
+        <v>0.001486041466705501</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.0002756569592747837</v>
+        <v>0.000257747364230454</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.000149382438394241</v>
+        <v>0.0005048420280218124</v>
       </c>
       <c r="EI16" t="n">
-        <v>6.649801798630506e-05</v>
+        <v>0.006359731778502464</v>
       </c>
       <c r="EJ16" t="n">
-        <v>4.363032712717541e-05</v>
+        <v>0.001064545474946499</v>
       </c>
       <c r="EK16" t="n">
-        <v>6.647517875535414e-05</v>
+        <v>0.0001836924348026514</v>
       </c>
       <c r="EL16" t="n">
-        <v>5.4616313718725e-05</v>
+        <v>9.509875235380605e-05</v>
       </c>
       <c r="EM16" t="n">
-        <v>3.601240678108297e-05</v>
+        <v>0.003984166774898767</v>
       </c>
       <c r="EN16" t="n">
-        <v>9.834096999838948e-06</v>
+        <v>0.0009772453922778368</v>
       </c>
       <c r="EO16" t="n">
-        <v>4.986789645045064e-05</v>
+        <v>0.001761772087775171</v>
       </c>
       <c r="EP16" t="n">
-        <v>9.860946738626808e-05</v>
+        <v>0.00497830705717206</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.0001270356879103929</v>
+        <v>0.0007484045345336199</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.0001499503414379433</v>
+        <v>8.321995846927166e-05</v>
       </c>
       <c r="ES16" t="n">
-        <v>6.153550930321217e-05</v>
+        <v>0.006208132021129131</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.0001875590241979808</v>
+        <v>0.0005459242966026068</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.0001249445194844157</v>
+        <v>0.002784020500257611</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.000273273151833564</v>
+        <v>0.0006168907857500017</v>
       </c>
       <c r="EW16" t="n">
-        <v>6.560361362062395e-05</v>
+        <v>0.0004701110301539302</v>
       </c>
       <c r="EX16" t="n">
-        <v>5.516736200661398e-05</v>
+        <v>0.0005728064570575953</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.0002098287950502709</v>
+        <v>0.007449375465512276</v>
       </c>
       <c r="EZ16" t="n">
-        <v>9.942929318640381e-05</v>
+        <v>0.000763442600145936</v>
       </c>
       <c r="FA16" t="n">
-        <v>5.85183224757202e-05</v>
+        <v>0.004513677675276995</v>
       </c>
       <c r="FB16" t="n">
-        <v>4.23315359512344e-05</v>
+        <v>0.0007085245451889932</v>
       </c>
       <c r="FC16" t="n">
-        <v>5.806428816867992e-05</v>
+        <v>0.002186693949624896</v>
       </c>
       <c r="FD16" t="n">
-        <v>9.166345989797264e-05</v>
+        <v>0.0007556581404060125</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.0001371666585328057</v>
+        <v>0.0005942537682130933</v>
       </c>
       <c r="FF16" t="n">
-        <v>6.731074245180935e-05</v>
+        <v>0.0005669551901519299</v>
       </c>
       <c r="FG16" t="n">
-        <v>6.524242053274065e-05</v>
+        <v>0.004008722957223654</v>
       </c>
       <c r="FH16" t="n">
-        <v>1.909596176119521e-05</v>
+        <v>0.003129926044493914</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.0001888299157144502</v>
+        <v>0.00246792146936059</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.0001350190723314881</v>
+        <v>0.004631336778402328</v>
       </c>
       <c r="FK16" t="n">
-        <v>9.524353663437068e-05</v>
+        <v>0.004282677546143532</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.0001530368463136256</v>
+        <v>0.009922003373503685</v>
       </c>
       <c r="FM16" t="n">
-        <v>9.04825355974026e-06</v>
+        <v>0.002126197330653667</v>
       </c>
       <c r="FN16" t="n">
-        <v>8.674968557897955e-05</v>
+        <v>0.004841370042413473</v>
       </c>
       <c r="FO16" t="n">
-        <v>9.114386921282858e-05</v>
+        <v>0.0132632814347744</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.0001873886358225718</v>
+        <v>0.00227740965783596</v>
       </c>
       <c r="FQ16" t="n">
-        <v>1.268000141863013e-05</v>
+        <v>0.002725484315305948</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.0002373519237153232</v>
+        <v>0.005492307245731354</v>
       </c>
       <c r="FS16" t="n">
-        <v>3.216198092559353e-05</v>
+        <v>0.001719006453640759</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.0001394146092934534</v>
+        <v>0.01482323743402958</v>
       </c>
       <c r="FU16" t="n">
-        <v>8.50199066917412e-05</v>
+        <v>0.003574260976165533</v>
       </c>
       <c r="FV16" t="n">
-        <v>3.862013545585796e-05</v>
+        <v>0.002040278632193804</v>
       </c>
       <c r="FW16" t="n">
-        <v>3.154301157337613e-05</v>
+        <v>0.01410950720310211</v>
       </c>
       <c r="FX16" t="n">
-        <v>6.404497980838642e-07</v>
+        <v>0.002436114009469748</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.0002285974042024463</v>
+        <v>0.004528482910245657</v>
       </c>
       <c r="FZ16" t="n">
-        <v>7.897333125583827e-05</v>
+        <v>0.001540771103464067</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.0001217801982420497</v>
+        <v>0.006005316972732544</v>
       </c>
       <c r="GB16" t="n">
-        <v>3.691863093990833e-05</v>
+        <v>0.0005631032399833202</v>
       </c>
       <c r="GC16" t="n">
-        <v>3.936543726013042e-05</v>
+        <v>0.009173291735351086</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.0001353735569864511</v>
+        <v>0.004546008538454771</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.0002530372003093362</v>
+        <v>0.004112889058887959</v>
       </c>
       <c r="GF16" t="n">
-        <v>4.344925400801003e-06</v>
+        <v>0.0008089393377304077</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.0001664117153268307</v>
+        <v>0.00323743955232203</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.0001071557926479727</v>
+        <v>9.03219277148537e-09</v>
       </c>
       <c r="B17" t="n">
-        <v>0.003763760672882199</v>
+        <v>9.609918194541933e-09</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0001003943252726458</v>
+        <v>3.167325068886839e-09</v>
       </c>
       <c r="D17" t="n">
-        <v>0.000618663732893765</v>
+        <v>3.639431866986342e-09</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001409779069945216</v>
+        <v>1.92147431299361e-09</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0004540873342193663</v>
+        <v>5.74459102509195e-09</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0002147593477275223</v>
+        <v>5.218177001609092e-10</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0004981828387826681</v>
+        <v>8.990373778772209e-09</v>
       </c>
       <c r="I17" t="n">
-        <v>1.687907570158131e-06</v>
+        <v>6.053891610235951e-09</v>
       </c>
       <c r="J17" t="n">
-        <v>7.233697397168726e-05</v>
+        <v>1.048977882334157e-08</v>
       </c>
       <c r="K17" t="n">
-        <v>0.003271653316915035</v>
+        <v>1.075924149773755e-08</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0005772492149844766</v>
+        <v>2.447517744030847e-09</v>
       </c>
       <c r="M17" t="n">
-        <v>5.923210119362921e-05</v>
+        <v>2.367275930836854e-09</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0009345510043203831</v>
+        <v>2.853810299185966e-09</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0006555125000886619</v>
+        <v>5.218900867021148e-09</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0002091272181132808</v>
+        <v>9.475585871498993e-10</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0001309218932874501</v>
+        <v>8.684731156449743e-09</v>
       </c>
       <c r="R17" t="n">
-        <v>1.94103158719372e-05</v>
+        <v>3.683746918614617e-10</v>
       </c>
       <c r="S17" t="n">
-        <v>3.667426062747836e-05</v>
+        <v>2.520891495549904e-09</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0004669094341807067</v>
+        <v>2.665520248967823e-09</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0001027482285280712</v>
+        <v>1.188782849936842e-09</v>
       </c>
       <c r="V17" t="n">
-        <v>0.000401489349314943</v>
+        <v>6.000793750793321e-10</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0006777074886485934</v>
+        <v>4.240070239358573e-10</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0001514817995484918</v>
+        <v>9.211012508281158e-10</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.203242759918794e-05</v>
+        <v>9.027658620652801e-10</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.0006200622883625329</v>
+        <v>4.903537131895064e-09</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.000167808699188754</v>
+        <v>2.753315131442946e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0002385679690632969</v>
+        <v>2.300967749668814e-10</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.512286300770938e-06</v>
+        <v>2.304876511871612e-09</v>
       </c>
       <c r="AD17" t="n">
-        <v>9.923285688273609e-05</v>
+        <v>3.006580095998856e-09</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.0001046802499331534</v>
+        <v>1.7193582113606e-09</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0001796048018150032</v>
+        <v>3.620903854528734e-10</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.635864413809031e-05</v>
+        <v>5.114297874087015e-10</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.421302921604365e-05</v>
+        <v>8.94579743615509e-10</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.0001437426108168438</v>
+        <v>2.454587422207055e-09</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.000313355412799865</v>
+        <v>3.476072318875367e-09</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.0006453327368944883</v>
+        <v>4.968891076373438e-09</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.0003845985920634121</v>
+        <v>3.845354590303884e-10</v>
       </c>
       <c r="AM17" t="n">
-        <v>8.854873885866255e-05</v>
+        <v>5.01758012916298e-09</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.823866841732524e-05</v>
+        <v>1.636276447669616e-09</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.0004183310375083238</v>
+        <v>1.573764868423311e-10</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.000349375099176541</v>
+        <v>2.112887087513116e-10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2.970378773170523e-05</v>
+        <v>5.981426465240247e-10</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.0001288561907131225</v>
+        <v>1.335680455127886e-09</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.945385004859418e-05</v>
+        <v>4.386496998964873e-10</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.231102502672002e-05</v>
+        <v>7.99842503340642e-09</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.00238535413518548</v>
+        <v>5.97599747464983e-11</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.0002964340965263546</v>
+        <v>2.940786725247335e-09</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.0002179553703172132</v>
+        <v>1.4864089958877e-09</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.0008795356843620539</v>
+        <v>6.486133852234843e-09</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.000428884057328105</v>
+        <v>3.068995890753712e-10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.0002983146696351469</v>
+        <v>9.532346023632954e-10</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.692324627190828e-05</v>
+        <v>7.146599423357713e-10</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.350799695705064e-05</v>
+        <v>7.55797202600661e-10</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.0004301667504478246</v>
+        <v>3.074341226039223e-09</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.0009378007962368429</v>
+        <v>8.926060779401723e-09</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.0005786654655821621</v>
+        <v>7.888126818400565e-10</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.0001051086073857732</v>
+        <v>3.23054405448886e-09</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.0006195071619004011</v>
+        <v>8.0270350366618e-09</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.0003036894195247442</v>
+        <v>4.543486475938607e-09</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.0004089735157322139</v>
+        <v>9.754281826701572e-10</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.0002189326623920351</v>
+        <v>4.524423946605793e-09</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.0001220748235937208</v>
+        <v>7.16858039595536e-09</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.0003221792576368898</v>
+        <v>3.285824390353298e-10</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.0006513269036076963</v>
+        <v>5.151996607111187e-10</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.0003410153149161488</v>
+        <v>1.595587550973221e-10</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.000161730931722559</v>
+        <v>8.129164563719371e-10</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.0003716500650625676</v>
+        <v>4.728735181203092e-10</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.0001722410816000775</v>
+        <v>1.490620515909313e-09</v>
       </c>
       <c r="BR17" t="n">
-        <v>1.588513259775937e-05</v>
+        <v>1.866480081602617e-09</v>
       </c>
       <c r="BS17" t="n">
-        <v>4.631396950571798e-05</v>
+        <v>7.339829855013136e-10</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.0001638652029214427</v>
+        <v>4.259484431834437e-11</v>
       </c>
       <c r="BU17" t="n">
-        <v>2.720327756833285e-05</v>
+        <v>6.276981601160969e-09</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.001463830703869462</v>
+        <v>5.787392232114996e-10</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.0002510285994503647</v>
+        <v>2.036004254080126e-09</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.0001088151402655058</v>
+        <v>2.617679406569096e-10</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.0005013115587644279</v>
+        <v>7.467256257776e-10</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.0001393640995956957</v>
+        <v>6.786032846761714e-10</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.0001874123991001397</v>
+        <v>7.154178360835317e-10</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.0001490004069637507</v>
+        <v>2.584120251114541e-09</v>
       </c>
       <c r="CC17" t="n">
-        <v>9.829936607275158e-05</v>
+        <v>2.609883698045934e-10</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.0001251371286343783</v>
+        <v>1.754351552918365e-09</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.000603804481215775</v>
+        <v>1.997242815576783e-09</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.0001434552104910836</v>
+        <v>8.563564302122018e-10</v>
       </c>
       <c r="CG17" t="n">
-        <v>9.235682227881625e-05</v>
+        <v>1.33861299822513e-09</v>
       </c>
       <c r="CH17" t="n">
-        <v>6.13599841017276e-05</v>
+        <v>1.258423920624807e-09</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.420110467937775e-05</v>
+        <v>2.603532500700112e-09</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.0001666667521931231</v>
+        <v>9.408487322559722e-10</v>
       </c>
       <c r="CK17" t="n">
-        <v>0.000102945756225381</v>
+        <v>1.95576929651331e-10</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.860640259110369e-05</v>
+        <v>5.414576564888307e-10</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.0008111097267828882</v>
+        <v>9.816600865519831e-10</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.0004894082085229456</v>
+        <v>2.637551732576071e-09</v>
       </c>
       <c r="CO17" t="n">
-        <v>0.0002448150771670043</v>
+        <v>3.769034417899775e-09</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.0002185261691920459</v>
+        <v>1.702989305130131e-09</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.0004335199191700667</v>
+        <v>4.361632832683426e-09</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.0004271009820513427</v>
+        <v>2.607932314546701e-09</v>
       </c>
       <c r="CS17" t="n">
-        <v>0.0005890383617952466</v>
+        <v>1.822140216489743e-09</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.0004368002410046756</v>
+        <v>2.405132093485918e-09</v>
       </c>
       <c r="CU17" t="n">
-        <v>0.0001044099917635322</v>
+        <v>2.183050629156469e-09</v>
       </c>
       <c r="CV17" t="n">
-        <v>0.0001059925270965323</v>
+        <v>1.367277624453322e-09</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.0004935808246955276</v>
+        <v>1.991609543949835e-09</v>
       </c>
       <c r="CX17" t="n">
-        <v>0.0002381197700742632</v>
+        <v>9.357840058399347e-10</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.0002811797894537449</v>
+        <v>1.271520111423285e-09</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.0001059227579389699</v>
+        <v>1.151918116448769e-09</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.344356041954597e-05</v>
+        <v>2.156865575031475e-09</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.0001385638315696269</v>
+        <v>2.192366843623006e-10</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.0001875861344160512</v>
+        <v>9.763597708101202e-10</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.460696876165457e-05</v>
+        <v>4.930125196977997e-10</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.0003633702581282705</v>
+        <v>6.144278974495876e-10</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.0006081474130041897</v>
+        <v>3.940600734608779e-09</v>
       </c>
       <c r="DG17" t="n">
-        <v>4.196845839032903e-05</v>
+        <v>6.454086598495223e-09</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.001332387677393854</v>
+        <v>5.866168661938786e-10</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.0006578752654604614</v>
+        <v>6.507535399435938e-09</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.0002744951052591205</v>
+        <v>1.251330844498355e-10</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.0002483233693055809</v>
+        <v>1.893737833214004e-09</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.0001095590487238951</v>
+        <v>2.75456235598881e-09</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.0002369619905948639</v>
+        <v>4.290795718731033e-09</v>
       </c>
       <c r="DN17" t="n">
-        <v>3.825238673016429e-05</v>
+        <v>1.937799476436908e-09</v>
       </c>
       <c r="DO17" t="n">
-        <v>7.029951666481793e-05</v>
+        <v>4.762513050593498e-09</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.0003920820308849216</v>
+        <v>2.400573961836017e-09</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.0002606711350381374</v>
+        <v>2.660202946813683e-09</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.0002516025269869715</v>
+        <v>1.93588123309496e-09</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.0002629123046062887</v>
+        <v>1.522514558871535e-09</v>
       </c>
       <c r="DT17" t="n">
-        <v>3.302382901892997e-05</v>
+        <v>7.090541487286828e-10</v>
       </c>
       <c r="DU17" t="n">
-        <v>6.515693530673161e-05</v>
+        <v>3.758334532477647e-09</v>
       </c>
       <c r="DV17" t="n">
-        <v>2.03973104362376e-06</v>
+        <v>1.077076094979645e-09</v>
       </c>
       <c r="DW17" t="n">
-        <v>1.819659883040003e-05</v>
+        <v>2.205762017482016e-09</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.000422840123064816</v>
+        <v>2.045813074502689e-09</v>
       </c>
       <c r="DY17" t="n">
-        <v>0.0002061964041786268</v>
+        <v>5.977340844509627e-11</v>
       </c>
       <c r="DZ17" t="n">
-        <v>1.844082726165652e-05</v>
+        <v>1.277816963352052e-09</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.0003822730213869363</v>
+        <v>9.168224401889802e-09</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.817420343286358e-05</v>
+        <v>2.716552982562348e-09</v>
       </c>
       <c r="EC17" t="n">
-        <v>9.776596562005579e-05</v>
+        <v>1.655752313034498e-09</v>
       </c>
       <c r="ED17" t="n">
-        <v>1.421897923137294e-05</v>
+        <v>1.66646052512931e-09</v>
       </c>
       <c r="EE17" t="n">
-        <v>3.833505616057664e-05</v>
+        <v>2.72977107584893e-09</v>
       </c>
       <c r="EF17" t="n">
-        <v>0.0004026192764285952</v>
+        <v>1.759474455020893e-09</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.0006427227053791285</v>
+        <v>5.673272407413776e-10</v>
       </c>
       <c r="EH17" t="n">
-        <v>4.48753016826231e-05</v>
+        <v>1.929931769950599e-09</v>
       </c>
       <c r="EI17" t="n">
-        <v>3.523622581269592e-06</v>
+        <v>7.197942242243016e-10</v>
       </c>
       <c r="EJ17" t="n">
-        <v>2.830377343343571e-05</v>
+        <v>4.768089811868492e-10</v>
       </c>
       <c r="EK17" t="n">
-        <v>6.651510921074077e-05</v>
+        <v>2.961099809795087e-09</v>
       </c>
       <c r="EL17" t="n">
-        <v>0.000111276785901282</v>
+        <v>1.534535137848181e-10</v>
       </c>
       <c r="EM17" t="n">
-        <v>0.0001259954151464626</v>
+        <v>5.60005375405126e-10</v>
       </c>
       <c r="EN17" t="n">
-        <v>3.918441871064715e-05</v>
+        <v>1.177192676671268e-09</v>
       </c>
       <c r="EO17" t="n">
-        <v>0.0001082850940292701</v>
+        <v>1.513121183904786e-09</v>
       </c>
       <c r="EP17" t="n">
-        <v>4.740314034279436e-05</v>
+        <v>1.121981285656659e-09</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0.0004618224920704961</v>
+        <v>1.591831111369402e-10</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.0003573750727809966</v>
+        <v>8.355648395408366e-10</v>
       </c>
       <c r="ES17" t="n">
-        <v>1.294149478781037e-05</v>
+        <v>1.509026459345364e-09</v>
       </c>
       <c r="ET17" t="n">
-        <v>7.988857396412641e-05</v>
+        <v>2.812833077570076e-09</v>
       </c>
       <c r="EU17" t="n">
-        <v>0.0002333267912035808</v>
+        <v>8.668498141517489e-10</v>
       </c>
       <c r="EV17" t="n">
-        <v>0.0004287801566533744</v>
+        <v>3.962029870852035e-10</v>
       </c>
       <c r="EW17" t="n">
-        <v>0.0002801576629281044</v>
+        <v>4.024030442195681e-09</v>
       </c>
       <c r="EX17" t="n">
-        <v>8.389602589886636e-05</v>
+        <v>1.791279791163447e-09</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.000531529076397419</v>
+        <v>2.850557567768419e-09</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0.0001904706150526181</v>
+        <v>4.908992101704257e-10</v>
       </c>
       <c r="FA17" t="n">
-        <v>3.068740261369385e-05</v>
+        <v>1.484422695874343e-09</v>
       </c>
       <c r="FB17" t="n">
-        <v>2.873656194424257e-05</v>
+        <v>1.338231081504659e-09</v>
       </c>
       <c r="FC17" t="n">
-        <v>7.301961159100756e-05</v>
+        <v>2.357402495434258e-09</v>
       </c>
       <c r="FD17" t="n">
-        <v>0.000197460554772988</v>
+        <v>6.365643567818324e-10</v>
       </c>
       <c r="FE17" t="n">
-        <v>0.0001099615546991117</v>
+        <v>1.498758117612908e-09</v>
       </c>
       <c r="FF17" t="n">
-        <v>5.020021853852086e-05</v>
+        <v>9.685638402423535e-11</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.0001238220575032756</v>
+        <v>9.653783328289478e-11</v>
       </c>
       <c r="FH17" t="n">
-        <v>4.372349940240383e-05</v>
+        <v>2.795391029764005e-09</v>
       </c>
       <c r="FI17" t="n">
-        <v>0.0003890067455358803</v>
+        <v>3.915750834693199e-09</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.000234909137361683</v>
+        <v>6.552930420511416e-10</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.0004273735103197396</v>
+        <v>4.869411096564136e-09</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.0002180851297453046</v>
+        <v>4.778678008854342e-10</v>
       </c>
       <c r="FM17" t="n">
-        <v>8.06684693088755e-05</v>
+        <v>2.81872358787183e-10</v>
       </c>
       <c r="FN17" t="n">
-        <v>0.0001046343095367774</v>
+        <v>3.981942775510561e-09</v>
       </c>
       <c r="FO17" t="n">
-        <v>0.0002803698880597949</v>
+        <v>9.03291774712045e-10</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.0004190173931419849</v>
+        <v>4.987882995521886e-09</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.0004190184990875423</v>
+        <v>5.508594025371849e-09</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.0004462547367438674</v>
+        <v>8.613867841233969e-09</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.0002472951891832054</v>
+        <v>5.76929259921144e-09</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.0001604892458999529</v>
+        <v>3.675810544834235e-09</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.0001798557786969468</v>
+        <v>1.876576449788558e-09</v>
       </c>
       <c r="FV17" t="n">
-        <v>2.583785499155056e-05</v>
+        <v>3.687792293760594e-09</v>
       </c>
       <c r="FW17" t="n">
-        <v>0.0001189406611956656</v>
+        <v>2.211497873716439e-09</v>
       </c>
       <c r="FX17" t="n">
-        <v>0.0001023912991513498</v>
+        <v>1.339755639762075e-09</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.0005313049769029021</v>
+        <v>1.79203374361947e-09</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.0002303626388311386</v>
+        <v>5.112609002821955e-09</v>
       </c>
       <c r="GA17" t="n">
-        <v>8.805331162875518e-05</v>
+        <v>3.78625575336855e-09</v>
       </c>
       <c r="GB17" t="n">
-        <v>0.000130282889585942</v>
+        <v>4.123171526426717e-10</v>
       </c>
       <c r="GC17" t="n">
-        <v>0.0002129645872628316</v>
+        <v>4.72115990746147e-09</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.0005879380623809993</v>
+        <v>1.605818811256654e-09</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.0004732507513836026</v>
+        <v>1.497607926559397e-09</v>
       </c>
       <c r="GF17" t="n">
-        <v>0.0002859037194866687</v>
+        <v>9.766571995584172e-10</v>
       </c>
       <c r="GG17" t="n">
-        <v>0.0002192962274421006</v>
+        <v>3.054560382409477e-09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6.442017820518231e-06</v>
+        <v>0.0002025330759352073</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0002863721747417003</v>
+        <v>0.002331252675503492</v>
       </c>
       <c r="C18" t="n">
-        <v>2.401361234660726e-05</v>
+        <v>0.0004072309820912778</v>
       </c>
       <c r="D18" t="n">
-        <v>0.000146484118886292</v>
+        <v>0.001798612647689879</v>
       </c>
       <c r="E18" t="n">
-        <v>6.153467256808653e-05</v>
+        <v>0.0006018471904098988</v>
       </c>
       <c r="F18" t="n">
-        <v>9.041828889166936e-06</v>
+        <v>0.002898079110309482</v>
       </c>
       <c r="G18" t="n">
-        <v>2.313373988727108e-05</v>
+        <v>0.0008071548072621226</v>
       </c>
       <c r="H18" t="n">
-        <v>2.663339728314895e-05</v>
+        <v>0.001064424403011799</v>
       </c>
       <c r="I18" t="n">
-        <v>2.444774690957274e-05</v>
+        <v>0.0006289922166615725</v>
       </c>
       <c r="J18" t="n">
-        <v>1.645748488954268e-05</v>
+        <v>0.0002203597396146506</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0002367689448874444</v>
+        <v>0.002523086033761501</v>
       </c>
       <c r="L18" t="n">
-        <v>1.263674676010851e-05</v>
+        <v>0.0006249478901736438</v>
       </c>
       <c r="M18" t="n">
-        <v>0.000129977153846994</v>
+        <v>0.0023042899556458</v>
       </c>
       <c r="N18" t="n">
-        <v>6.632672011619434e-05</v>
+        <v>0.0005545609164983034</v>
       </c>
       <c r="O18" t="n">
-        <v>4.049986819154583e-05</v>
+        <v>0.003207285422831774</v>
       </c>
       <c r="P18" t="n">
-        <v>1.500518192187883e-05</v>
+        <v>0.000852480879984796</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.165763337165117e-05</v>
+        <v>0.0004986394196748734</v>
       </c>
       <c r="R18" t="n">
-        <v>4.283268026483711e-06</v>
+        <v>0.0002287719398736954</v>
       </c>
       <c r="S18" t="n">
-        <v>1.198464633489493e-05</v>
+        <v>8.463766425848007e-05</v>
       </c>
       <c r="T18" t="n">
-        <v>4.330579758970998e-05</v>
+        <v>2.272051642648876e-05</v>
       </c>
       <c r="U18" t="n">
-        <v>8.723400242161006e-06</v>
+        <v>0.000363112660124898</v>
       </c>
       <c r="V18" t="n">
-        <v>1.245999101229245e-05</v>
+        <v>2.181799936806783e-05</v>
       </c>
       <c r="W18" t="n">
-        <v>1.43834749906091e-05</v>
+        <v>7.52006599213928e-06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.577614966663532e-05</v>
+        <v>0.0006677962373942137</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.931063863798045e-05</v>
+        <v>0.0002696338051464409</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.049542829103302e-05</v>
+        <v>0.0006976164877414703</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.696825868042652e-05</v>
+        <v>8.829064609017223e-05</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.056614903267473e-05</v>
+        <v>0.0004847976379096508</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.933857078664005e-05</v>
+        <v>0.0002007318835239857</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.985619514423888e-06</v>
+        <v>0.0004594616184476763</v>
       </c>
       <c r="AE18" t="n">
-        <v>6.036527338437736e-06</v>
+        <v>0.0004516582121141255</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.747568148857681e-06</v>
+        <v>0.0001935524778673425</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.383795390414889e-06</v>
+        <v>0.001437468687072396</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.849391264840961e-05</v>
+        <v>0.0001565528073115274</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.171216808870668e-06</v>
+        <v>0.001571637345477939</v>
       </c>
       <c r="AJ18" t="n">
-        <v>6.098624908190686e-06</v>
+        <v>1.313615757680964e-05</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.870009509730153e-05</v>
+        <v>0.0002351379807805642</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.72459838015493e-05</v>
+        <v>0.0004597515217028558</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.402278758177999e-05</v>
+        <v>0.0004837661399506032</v>
       </c>
       <c r="AN18" t="n">
-        <v>7.933617780508939e-06</v>
+        <v>0.0002106381871271878</v>
       </c>
       <c r="AO18" t="n">
-        <v>2.409964690741617e-05</v>
+        <v>0.0001220377598656341</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.456333459122106e-05</v>
+        <v>0.0002869983145501465</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.200053495471366e-05</v>
+        <v>0.0001174992576125078</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.781671562639531e-05</v>
+        <v>0.0005344330566003919</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.314989034057362e-06</v>
+        <v>0.000494417967274785</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.627584060770459e-05</v>
+        <v>0.0004259514389559627</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.0002064862055703998</v>
+        <v>0.001023262389935553</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.989511995110661e-05</v>
+        <v>0.0008115317323245108</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.134934740955941e-05</v>
+        <v>0.0004988780128769577</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.537935754138744e-06</v>
+        <v>0.002173120621591806</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.471780797146494e-05</v>
+        <v>0.001878984156064689</v>
       </c>
       <c r="AZ18" t="n">
-        <v>9.634991329221521e-07</v>
+        <v>0.0002249786339234561</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.736108788463753e-05</v>
+        <v>0.0003290206077508628</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.191150881320937e-07</v>
+        <v>0.0001776582939783111</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.674134339031298e-05</v>
+        <v>0.0001330259983660653</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.853964856010862e-05</v>
+        <v>0.0006996459560468793</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.768240953329951e-05</v>
+        <v>0.0004344907647464424</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.261962410761043e-05</v>
+        <v>0.0008482897537760437</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.812494055135176e-05</v>
+        <v>0.001005039317533374</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.339020622661337e-05</v>
+        <v>0.0002592088421806693</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.49870575114619e-05</v>
+        <v>0.0002817293861880898</v>
       </c>
       <c r="BJ18" t="n">
-        <v>2.836446583387442e-05</v>
+        <v>0.0009311899775639176</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.432743283658056e-05</v>
+        <v>0.0005308211548253894</v>
       </c>
       <c r="BL18" t="n">
-        <v>3.661177106550895e-05</v>
+        <v>7.932670996524394e-05</v>
       </c>
       <c r="BM18" t="n">
-        <v>3.97419098590035e-05</v>
+        <v>0.0001069732243195176</v>
       </c>
       <c r="BN18" t="n">
-        <v>2.96810976578854e-05</v>
+        <v>7.137720967875794e-05</v>
       </c>
       <c r="BO18" t="n">
-        <v>6.208286322362255e-06</v>
+        <v>0.0004176460788585246</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.205659231753089e-05</v>
+        <v>0.0001430395495845005</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.975568011403084e-05</v>
+        <v>0.0004236368113197386</v>
       </c>
       <c r="BR18" t="n">
-        <v>1.240523488377221e-05</v>
+        <v>0.000234809354878962</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.312837048317306e-05</v>
+        <v>4.785630153492093e-05</v>
       </c>
       <c r="BT18" t="n">
-        <v>1.967105345102027e-05</v>
+        <v>0.0003833950613625348</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.42190629048855e-05</v>
+        <v>0.0001444208464818075</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.0001091546000679955</v>
+        <v>0.0007490428979508579</v>
       </c>
       <c r="BW18" t="n">
-        <v>2.68242038146127e-05</v>
+        <v>0.0003930985985789448</v>
       </c>
       <c r="BX18" t="n">
-        <v>1.829354005167261e-05</v>
+        <v>0.0004903918015770614</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.704925125523005e-05</v>
+        <v>0.0002939659461844712</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.383646278758533e-05</v>
+        <v>0.001330139464698732</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.44875075420714e-05</v>
+        <v>0.0003998809261247516</v>
       </c>
       <c r="CB18" t="n">
-        <v>6.459311407525092e-06</v>
+        <v>0.0003330633044242859</v>
       </c>
       <c r="CC18" t="n">
-        <v>1.941827213158831e-05</v>
+        <v>0.0001176654623122886</v>
       </c>
       <c r="CD18" t="n">
-        <v>1.767105686667492e-06</v>
+        <v>0.0001401119079673663</v>
       </c>
       <c r="CE18" t="n">
-        <v>5.057840098743327e-05</v>
+        <v>0.0006899647414684296</v>
       </c>
       <c r="CF18" t="n">
-        <v>1.120424167311285e-05</v>
+        <v>0.0001224714069394395</v>
       </c>
       <c r="CG18" t="n">
-        <v>1.368613447993994e-05</v>
+        <v>0.0005885752034373581</v>
       </c>
       <c r="CH18" t="n">
-        <v>8.183031241060235e-06</v>
+        <v>0.0001951901940628886</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.215379481640412e-06</v>
+        <v>0.0007522414671257138</v>
       </c>
       <c r="CJ18" t="n">
-        <v>9.651153959566727e-06</v>
+        <v>8.903585694497451e-06</v>
       </c>
       <c r="CK18" t="n">
-        <v>2.809857733154786e-06</v>
+        <v>0.000258034560829401</v>
       </c>
       <c r="CL18" t="n">
-        <v>8.843458090268541e-06</v>
+        <v>0.0004076711484231055</v>
       </c>
       <c r="CM18" t="n">
-        <v>5.656995926983654e-05</v>
+        <v>0.0001260051503777504</v>
       </c>
       <c r="CN18" t="n">
-        <v>4.365485801827163e-05</v>
+        <v>2.758202026598155e-05</v>
       </c>
       <c r="CO18" t="n">
-        <v>3.813488547166344e-07</v>
+        <v>0.001060996204614639</v>
       </c>
       <c r="CP18" t="n">
-        <v>4.722052835859358e-05</v>
+        <v>0.0007713855593465269</v>
       </c>
       <c r="CQ18" t="n">
-        <v>5.602783494396135e-05</v>
+        <v>0.001051812432706356</v>
       </c>
       <c r="CR18" t="n">
-        <v>2.296486854902469e-05</v>
+        <v>0.0003363441210240126</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.781986015383154e-05</v>
+        <v>8.542151772417128e-05</v>
       </c>
       <c r="CT18" t="n">
-        <v>4.640010229195468e-05</v>
+        <v>5.368312122300267e-05</v>
       </c>
       <c r="CU18" t="n">
-        <v>2.92439244731213e-06</v>
+        <v>0.0004349829105194658</v>
       </c>
       <c r="CV18" t="n">
-        <v>3.300752268842189e-06</v>
+        <v>0.000216043641557917</v>
       </c>
       <c r="CW18" t="n">
-        <v>4.417302261572331e-05</v>
+        <v>0.0006181696662679315</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.950722617038991e-05</v>
+        <v>0.0001869118132162839</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.478278656781185e-05</v>
+        <v>0.0006474026013165712</v>
       </c>
       <c r="CZ18" t="n">
-        <v>1.064850584953092e-05</v>
+        <v>9.215523459715769e-05</v>
       </c>
       <c r="DA18" t="n">
-        <v>7.85783413448371e-06</v>
+        <v>0.0008065270958468318</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.062711635313462e-05</v>
+        <v>4.417871969053522e-05</v>
       </c>
       <c r="DC18" t="n">
-        <v>5.986310043226695e-06</v>
+        <v>0.0002413195616099983</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.056464720430085e-06</v>
+        <v>0.0003777742094825953</v>
       </c>
       <c r="DE18" t="n">
-        <v>2.117702024406753e-05</v>
+        <v>0.0002279159525642172</v>
       </c>
       <c r="DF18" t="n">
-        <v>2.988942469528411e-05</v>
+        <v>0.0006643338711000979</v>
       </c>
       <c r="DG18" t="n">
-        <v>7.5432376434037e-07</v>
+        <v>0.0005488356109708548</v>
       </c>
       <c r="DH18" t="n">
-        <v>6.347607268253341e-05</v>
+        <v>0.0002457060036249459</v>
       </c>
       <c r="DI18" t="n">
-        <v>3.526971113387845e-06</v>
+        <v>0.0008123180596157908</v>
       </c>
       <c r="DJ18" t="n">
-        <v>6.564097930095159e-06</v>
+        <v>0.001171590178273618</v>
       </c>
       <c r="DK18" t="n">
-        <v>1.063837225956377e-05</v>
+        <v>0.0003157884930260479</v>
       </c>
       <c r="DL18" t="n">
-        <v>1.295704350923188e-05</v>
+        <v>0.0004601976834237576</v>
       </c>
       <c r="DM18" t="n">
-        <v>9.235388461092953e-06</v>
+        <v>0.0003816056414507329</v>
       </c>
       <c r="DN18" t="n">
-        <v>7.386372544715414e-07</v>
+        <v>0.0002840352244675159</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.552903813717421e-05</v>
+        <v>0.0007040598429739475</v>
       </c>
       <c r="DP18" t="n">
-        <v>1.379065361106768e-05</v>
+        <v>0.0003897809074260294</v>
       </c>
       <c r="DQ18" t="n">
-        <v>1.744052678986918e-05</v>
+        <v>0.0004332236130721867</v>
       </c>
       <c r="DR18" t="n">
-        <v>2.77257331617875e-05</v>
+        <v>0.0001920026843436062</v>
       </c>
       <c r="DS18" t="n">
-        <v>4.108700522920117e-06</v>
+        <v>0.0001349168596789241</v>
       </c>
       <c r="DT18" t="n">
-        <v>1.785206336535339e-06</v>
+        <v>0.0005292266723699868</v>
       </c>
       <c r="DU18" t="n">
-        <v>1.369268920825562e-05</v>
+        <v>0.0005912285996600986</v>
       </c>
       <c r="DV18" t="n">
-        <v>1.545342092867941e-05</v>
+        <v>0.0003370612394064665</v>
       </c>
       <c r="DW18" t="n">
-        <v>1.150505113400868e-08</v>
+        <v>0.0002399684890406206</v>
       </c>
       <c r="DX18" t="n">
-        <v>2.174250766984187e-05</v>
+        <v>0.0003498922451399267</v>
       </c>
       <c r="DY18" t="n">
-        <v>1.284546306123957e-05</v>
+        <v>0.0007497173501178622</v>
       </c>
       <c r="DZ18" t="n">
-        <v>1.094934668799397e-05</v>
+        <v>4.023220390081406e-05</v>
       </c>
       <c r="EA18" t="n">
-        <v>1.999228152271826e-05</v>
+        <v>0.0002130785869667307</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.399876873620087e-05</v>
+        <v>9.837800462264568e-05</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.0950133400911e-05</v>
+        <v>0.0001972486788872629</v>
       </c>
       <c r="ED18" t="n">
-        <v>3.943838692066493e-06</v>
+        <v>0.0004764875047840178</v>
       </c>
       <c r="EE18" t="n">
-        <v>9.15993780381541e-07</v>
+        <v>0.0007752396631985903</v>
       </c>
       <c r="EF18" t="n">
-        <v>1.06929201137973e-06</v>
+        <v>0.0001171917392639443</v>
       </c>
       <c r="EG18" t="n">
-        <v>5.032363696955144e-05</v>
+        <v>0.0004455583693925291</v>
       </c>
       <c r="EH18" t="n">
-        <v>1.820359830162488e-05</v>
+        <v>0.0003960151225328445</v>
       </c>
       <c r="EI18" t="n">
-        <v>1.974702718143817e-05</v>
+        <v>0.0002336551842745394</v>
       </c>
       <c r="EJ18" t="n">
-        <v>3.825913518085144e-05</v>
+        <v>9.485639748163521e-05</v>
       </c>
       <c r="EK18" t="n">
-        <v>5.694280844181776e-06</v>
+        <v>0.0006496038404293358</v>
       </c>
       <c r="EL18" t="n">
-        <v>4.745534624817083e-06</v>
+        <v>2.774247695924714e-05</v>
       </c>
       <c r="EM18" t="n">
-        <v>7.166870091168676e-06</v>
+        <v>7.7746735769324e-06</v>
       </c>
       <c r="EN18" t="n">
-        <v>4.818975867237896e-06</v>
+        <v>0.0001293493696721271</v>
       </c>
       <c r="EO18" t="n">
-        <v>3.173127879563253e-06</v>
+        <v>0.0003134692087769508</v>
       </c>
       <c r="EP18" t="n">
-        <v>3.456962804193608e-05</v>
+        <v>0.0005254872958175838</v>
       </c>
       <c r="EQ18" t="n">
-        <v>2.925744593085255e-05</v>
+        <v>0.0003929999656975269</v>
       </c>
       <c r="ER18" t="n">
-        <v>9.911864253808744e-06</v>
+        <v>0.0005879352102056146</v>
       </c>
       <c r="ES18" t="n">
-        <v>6.280212801357266e-06</v>
+        <v>0.0004119261866435409</v>
       </c>
       <c r="ET18" t="n">
-        <v>1.358893314318266e-05</v>
+        <v>0.0001987233990803361</v>
       </c>
       <c r="EU18" t="n">
-        <v>2.112022593792062e-05</v>
+        <v>0.0002075247030006722</v>
       </c>
       <c r="EV18" t="n">
-        <v>2.030916402873117e-05</v>
+        <v>0.0005167583003640175</v>
       </c>
       <c r="EW18" t="n">
-        <v>1.013526707538404e-05</v>
+        <v>0.0001537986099720001</v>
       </c>
       <c r="EX18" t="n">
-        <v>4.257558430253994e-06</v>
+        <v>0.0001862328790593892</v>
       </c>
       <c r="EY18" t="n">
-        <v>4.693352457252331e-05</v>
+        <v>0.0008224385092034936</v>
       </c>
       <c r="EZ18" t="n">
-        <v>1.10009214040474e-05</v>
+        <v>0.0001262318110093474</v>
       </c>
       <c r="FA18" t="n">
-        <v>1.95799620996695e-05</v>
+        <v>0.0007019022013992071</v>
       </c>
       <c r="FB18" t="n">
-        <v>4.901214197161607e-06</v>
+        <v>0.000172709027538076</v>
       </c>
       <c r="FC18" t="n">
-        <v>8.087708010862116e-06</v>
+        <v>0.0007445711526088417</v>
       </c>
       <c r="FD18" t="n">
-        <v>1.081092614185764e-05</v>
+        <v>3.262810059823096e-05</v>
       </c>
       <c r="FE18" t="n">
-        <v>1.929443214976345e-06</v>
+        <v>0.0001957905333256349</v>
       </c>
       <c r="FF18" t="n">
-        <v>7.930967512947973e-06</v>
+        <v>0.0001941945811267942</v>
       </c>
       <c r="FG18" t="n">
-        <v>1.042373969539767e-05</v>
+        <v>9.72770358202979e-05</v>
       </c>
       <c r="FH18" t="n">
-        <v>1.189262275147485e-05</v>
+        <v>0.0005573762464337051</v>
       </c>
       <c r="FI18" t="n">
-        <v>2.794696411001496e-05</v>
+        <v>0.0009505546768195927</v>
       </c>
       <c r="FJ18" t="n">
-        <v>2.935197335318662e-05</v>
+        <v>0.0004700365825556219</v>
       </c>
       <c r="FK18" t="n">
-        <v>1.942399103427306e-05</v>
+        <v>7.323105819523335e-06</v>
       </c>
       <c r="FL18" t="n">
-        <v>9.735737876326311e-06</v>
+        <v>0.001026987098157406</v>
       </c>
       <c r="FM18" t="n">
-        <v>1.409886226610979e-05</v>
+        <v>3.905243647750467e-05</v>
       </c>
       <c r="FN18" t="n">
-        <v>9.617958767194068e-07</v>
+        <v>0.0004900905769318342</v>
       </c>
       <c r="FO18" t="n">
-        <v>5.32834155819728e-06</v>
+        <v>0.0009266034467145801</v>
       </c>
       <c r="FP18" t="n">
-        <v>1.83700230991235e-05</v>
+        <v>0.0001628367317607626</v>
       </c>
       <c r="FQ18" t="n">
-        <v>3.649226709967479e-05</v>
+        <v>3.627231490099803e-05</v>
       </c>
       <c r="FR18" t="n">
-        <v>2.705362931010313e-05</v>
+        <v>0.001393350306898355</v>
       </c>
       <c r="FS18" t="n">
-        <v>1.333905856881756e-06</v>
+        <v>2.80027961707674e-06</v>
       </c>
       <c r="FT18" t="n">
-        <v>3.335274959681556e-05</v>
+        <v>0.0002567514311522245</v>
       </c>
       <c r="FU18" t="n">
-        <v>2.486020093783736e-05</v>
+        <v>0.0001279128773603588</v>
       </c>
       <c r="FV18" t="n">
-        <v>4.747156708617695e-06</v>
+        <v>0.0002808886056300253</v>
       </c>
       <c r="FW18" t="n">
-        <v>5.74141631659586e-06</v>
+        <v>0.0005436072242446244</v>
       </c>
       <c r="FX18" t="n">
-        <v>1.583550510986242e-05</v>
+        <v>9.398545080330223e-05</v>
       </c>
       <c r="FY18" t="n">
-        <v>3.594693771447055e-05</v>
+        <v>0.0002171435917261988</v>
       </c>
       <c r="FZ18" t="n">
-        <v>6.433328962884843e-06</v>
+        <v>0.0005645558703690767</v>
       </c>
       <c r="GA18" t="n">
-        <v>3.902956905221799e-06</v>
+        <v>0.0008931442862376571</v>
       </c>
       <c r="GB18" t="n">
-        <v>9.53591734287329e-06</v>
+        <v>0.0002090305933961645</v>
       </c>
       <c r="GC18" t="n">
-        <v>5.152908670424949e-06</v>
+        <v>0.001611347193829715</v>
       </c>
       <c r="GD18" t="n">
-        <v>4.183062992524356e-05</v>
+        <v>0.001204248750582337</v>
       </c>
       <c r="GE18" t="n">
-        <v>6.489284714916721e-05</v>
+        <v>4.07486513722688e-05</v>
       </c>
       <c r="GF18" t="n">
-        <v>1.551291279611178e-05</v>
+        <v>0.0001931174483615905</v>
       </c>
       <c r="GG18" t="n">
-        <v>1.998158404603601e-05</v>
+        <v>1.817611882870551e-05</v>
       </c>
     </row>
     <row r="19">
